--- a/veille-emploi/data/offres.xlsx
+++ b/veille-emploi/data/offres.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -462,22 +462,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43</t>
+          <t>2026-09-11 14:08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Concepteur Applicatifs de Tests F/H</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/4/ef70b806a9ddf422bb666554b9210fc3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9tYW5wb3dlci05NDE3MS5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
+          <t>https://apply.indeed.com/indeedapply/confirmemail/viewjob?iaUid=1k28cm5dnkhdu801&amp;apiToken=6e4168159714a741b7dd5372bed1a1816600d76a9cf78120927acd91b7cf04f4&amp;next=https%3A%2F%2Ffr.indeed.com%2Fviewjob%3Fjk%3D0ab73c27311da341</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -485,22 +485,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 11:43</t>
+          <t>2026-09-11 14:08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail H/F</t>
+          <t>Apprenez à reconnaître les emails frauduleux</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/5/bfaa369f3087e6282eba82fd3829c7c8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://apply.indeed.com/indeedapply/confirmemail/fraudlink?iaUid=1k28cm5dnkhdu801&amp;apiToken=6e4168159714a741b7dd5372bed1a1816600d76a9cf78120927acd91b7cf04f4</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/7/7ec2d07e9b42f51a7efb9cba12cee843/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/4/ef70b806a9ddf422bb666554b9210fc3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9tYW5wb3dlci05NDE3MS5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
+          <t>Ingénieur Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/8/347975af4abe46f37b18c2794e2ee0ec/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/5/bfaa369f3087e6282eba82fd3829c7c8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/10/d9554946be02081e4097192267e529ec/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/7/7ec2d07e9b42f51a7efb9cba12cee843/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Modern Workplace Confirmé H/F</t>
+          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/11/5a6a621e76f1816bccd0d3ea8436d98c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/8/347975af4abe46f37b18c2794e2ee0ec/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/13/4e15ee690ae255951de2514fc05cd1ca/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/10/d9554946be02081e4097192267e529ec/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -628,7 +628,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
+          <t>Ingénieur Modern Workplace Confirmé H/F</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/14/042e14b3f30f2494cb550934bef9da3c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/11/5a6a621e76f1816bccd0d3ea8436d98c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/16/32e20d40b939459f022e865d5bf19a94/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/13/4e15ee690ae255951de2514fc05cd1ca/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
+          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/17/d7e4c9ca3397c772428436b865a38c20/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/14/042e14b3f30f2494cb550934bef9da3c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -707,7 +707,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/19/ac73aa5c8d92e2d25a06026093928a2e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/16/32e20d40b939459f022e865d5bf19a94/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/32/6419657ddb431864f826bd63acc23456/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/17/d7e4c9ca3397c772428436b865a38c20/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/33/dd0b79a46834e1c7995be8f4a70deb36/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/19/ac73aa5c8d92e2d25a06026093928a2e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/4/82142203c8954033735661b1bbabd6d4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9hcy1pbnRlcm5hdGlvbmFsLTEyMzMxMi5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/32/6419657ddb431864f826bd63acc23456/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/5/672f54652a7c53800452952ee61e8cf3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/279aab4c-cfcd-4483-84bc-50ae66c05f9e/33/dd0b79a46834e1c7995be8f4a70deb36/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/7/e0f0dbf534f71727ab29e63e2f237ca1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/4/82142203c8954033735661b1bbabd6d4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9hcy1pbnRlcm5hdGlvbmFsLTEyMzMxMi5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
+          <t>Ingénieur Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/8/3260107f0dfe89a0e560dec8998b6020/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/5/672f54652a7c53800452952ee61e8cf3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/10/3d767d057c0607c67752fdbe4eaa01bf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/7/e0f0dbf534f71727ab29e63e2f237ca1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Modern Workplace Confirmé H/F</t>
+          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/11/d92e1ff8c424ef93007a117666daf519/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/8/3260107f0dfe89a0e560dec8998b6020/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/13/1740120ba6e3c1abe643ebd1811aa5a1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/10/3d767d057c0607c67752fdbe4eaa01bf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
+          <t>Ingénieur Modern Workplace Confirmé H/F</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/14/217be86fa1df78d2cf10deb1dbf85d08/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/11/d92e1ff8c424ef93007a117666daf519/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -960,7 +960,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/16/5c1331c8c41ae6a9d956c341b1525568/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/13/1740120ba6e3c1abe643ebd1811aa5a1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
+          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/17/1c3e2ce3425f77108febf68a3129c58f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/14/217be86fa1df78d2cf10deb1dbf85d08/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/19/ec8e3824e35b645fa4f06455a82a9371/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/16/5c1331c8c41ae6a9d956c341b1525568/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/32/b3952fa012072eb8393ee2118236f43a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/17/1c3e2ce3425f77108febf68a3129c58f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/33/6b188460110fb81af8441cfd5da0248b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/19/ec8e3824e35b645fa4f06455a82a9371/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail H/F</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/3/b77f395e3bbc4a0fc4ff77b0186cebe5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/32/b3952fa012072eb8393ee2118236f43a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/5/8ac6b9951dee1aa8bd5a398fb83c4311/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/7d8f8117-0c68-4af4-b239-0aee6021400e/33/6b188460110fb81af8441cfd5da0248b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
+          <t>Ingénieur Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/6/77af0be94bf37b8dbb2535226077f4a6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/3/b77f395e3bbc4a0fc4ff77b0186cebe5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/8/e1df51c8b34e443934838359c813a8dd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/5/8ac6b9951dee1aa8bd5a398fb83c4311/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Modern Workplace Confirmé H/F</t>
+          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/9/fb1bd8ba3c4aea973f84633c1a746929/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/6/77af0be94bf37b8dbb2535226077f4a6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/11/0efc6bc8afb6f2d6e8f9fce9b9424981/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/8/e1df51c8b34e443934838359c813a8dd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
+          <t>Ingénieur Modern Workplace Confirmé H/F</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/12/950034407ffec909afb4145eea043852/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/9/fb1bd8ba3c4aea973f84633c1a746929/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/14/841ea65b13d7fea9a03f4d40adfc54e3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/11/0efc6bc8afb6f2d6e8f9fce9b9424981/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
+          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/15/1d85fc5ca1c35e9369b47c2eac65ac72/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/12/950034407ffec909afb4145eea043852/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/17/ce46a4f84fd479a86a9514bf4d4dba51/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/14/841ea65b13d7fea9a03f4d40adfc54e3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/30/544b721f650ebcd703f1f2279b1cad9e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmw</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/15/1d85fc5ca1c35e9369b47c2eac65ac72/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/31/e27d46b4ae0339e393ca4b7bcf9543c6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZVVybCZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/17/ce46a4f84fd479a86a9514bf4d4dba51/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmwmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail H/F</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/3/8d922a273e2f4d99ee06bb0ce5e785cb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/30/544b721f650ebcd703f1f2279b1cad9e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmVVcmw</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/5/4868ad6a6505ff219b5dbea8a40d5db2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8b3a3bb-40ab-4bb1-b0d4-cee8dfac5d19/31/e27d46b4ae0339e393ca4b7bcf9543c6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZVVybCZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Expert·e Poste de Travail - Si Sensible H/F</t>
+          <t>Ingénieur Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/6/b8e2e31a48b5a53f777f14a7508d4da2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTI5NjY2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1Mjk2NjYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/3/8d922a273e2f4d99ee06bb0ce5e785cb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/8/dff9d954064cb23192d8bbbeeceeff75/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTI5NjY2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1Mjk2NjYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/5/4868ad6a6505ff219b5dbea8a40d5db2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Modern Workplace Confirmé H/F</t>
+          <t>Expert·e Poste de Travail - Si Sensible H/F</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/9/3fa85a6ec18778df67f1c0aabc7053bc/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/6/b8e2e31a48b5a53f777f14a7508d4da2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTI5NjY2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1Mjk2NjYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/11/9099c83b44171cc97dd18c9c4cb6c77a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/8/dff9d954064cb23192d8bbbeeceeff75/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTI5NjY2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1Mjk2NjYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
+          <t>Ingénieur Modern Workplace Confirmé H/F</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/12/b6e7a266a1f13d87ded4661515d8eefa/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/9/3fa85a6ec18778df67f1c0aabc7053bc/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/14/01b05051ec90f8ca5d5ff8cca6b17256/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/11/9099c83b44171cc97dd18c9c4cb6c77a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
+          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/15/7164828ce8022169405aecb6648ee342/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/12/b6e7a266a1f13d87ded4661515d8eefa/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/17/54ce7745be75102d0eaf1872d0130b0d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/14/01b05051ec90f8ca5d5ff8cca6b17256/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/30/e30c3422b1aec7acd516d527800e34aa/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/15/7164828ce8022169405aecb6648ee342/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/31/f72c44d6dc8042d226f99d7fe3f56ab8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/17/54ce7745be75102d0eaf1872d0130b0d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/4/80f0a761a7ad3ebba7972951fcfbc3dd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9uZW9zb2Z0LTM0NjgwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX2NvbnRlbnQ9dG91dHNhdm9pcnN1cmxlbnRyZXByaXNlI3RvdXRzYXZvaXJzdXJsZW50cmVwcmlzZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/30/e30c3422b1aec7acd516d527800e34aa/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur·e Poste de Travail Windows H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/5/1d5e7007841abc58b9ec8f13af19943f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/c9971b52-ae8b-4b0f-a40c-302bce1d6a22/31/f72c44d6dc8042d226f99d7fe3f56ab8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/7/ab48898f0c91a8442fcd2fc2771849d6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/4/80f0a761a7ad3ebba7972951fcfbc3dd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9uZW9zb2Z0LTM0NjgwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX2NvbnRlbnQ9dG91dHNhdm9pcnN1cmxlbnRyZXByaXNlI3RvdXRzYXZvaXJzdXJsZW50cmVwcmlzZQ</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail H/F</t>
+          <t>Ingénieur·e Poste de Travail Windows H/F</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/8/3b3f9f72aa45b6f4acda1513f6c4150d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/5/1d5e7007841abc58b9ec8f13af19943f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/10/82cda3a813e88ac8cdb500636e1abdd9/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/7/ab48898f0c91a8442fcd2fc2771849d6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Ingénieur Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/23/6cf078efb9a10d7ee8522428fdc3e617/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/8/3b3f9f72aa45b6f4acda1513f6c4150d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/24/ad923ce845957ec702d82cfdc1915e62/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/10/82cda3a813e88ac8cdb500636e1abdd9/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail H/F</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/3/bd3c35e7616ed9157e2cbe78320b32ef/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/23/6cf078efb9a10d7ee8522428fdc3e617/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/5/3b6fba8259eb54ef12297f782b130ce2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/62b6728b-f88e-4fd5-b1a5-602613985594/24/ad923ce845957ec702d82cfdc1915e62/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
+          <t>Ingénieur Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/6/7d5132c63c618eb2247cbd4f14c989c2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/3/bd3c35e7616ed9157e2cbe78320b32ef/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/8/209ce7047af78d82b691dea453e2d130/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/5/3b6fba8259eb54ef12297f782b130ce2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxNTM0NzExLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODE1MzQ3MTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Modern Workplace Confirmé H/F</t>
+          <t>Chef-Fe de Projet Technique - Ingénierie Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/9/97f4320b3c520d41bbabac442e4bede1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/6/7d5132c63c618eb2247cbd4f14c989c2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/11/b8f41c5c95741a66efea9ae44704764e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/8/209ce7047af78d82b691dea453e2d130/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwNTQxMzM0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODA1NDEzMzQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
+          <t>Ingénieur Modern Workplace Confirmé H/F</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/12/64428043b00def84550ea4dbf7ad5ea6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/9/97f4320b3c520d41bbabac442e4bede1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/14/3e58fc90ec8541538a153bd2c539314f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/11/b8f41c5c95741a66efea9ae44704764e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2NzEwMDQzLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzY3MTAwNDMmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
+          <t>Ingénieur Poste de Travail Ingénierie Plm - CAO - Calculs H/F</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/15/c5c14d6d43a117fa335603910c0175cb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/12/64428043b00def84550ea4dbf7ad5ea6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/17/dcc6adfdab5439bfac7bbe923b37ec99/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/14/3e58fc90ec8541538a153bd2c539314f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMzAyMzM1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIzMDIzMzUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Expert Poste de Travail Sccm - Mecm H/F</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/30/6c5d6f9d3d18c7563e5242657dfd95be/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/15/c5c14d6d43a117fa335603910c0175cb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/31/f37c5cdfad5840a486e2fd0da67f08a5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/17/dcc6adfdab5439bfac7bbe923b37ec99/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc2MzgxMDQ5Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzYzODEwNDkmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/4/c1714f6acc5d7a0bc9bb829fa7aaa4ac/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9hcy1pbnRlcm5hdGlvbmFsLTEyMzMxMi5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/30/6c5d6f9d3d18c7563e5242657dfd95be/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur·e Poste de Travail Windows H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/5/4c061858c84ea2ef8fcf32103b44b2e4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/078f03d0-88ee-4e35-9daa-0dfcf788dd70/31/f37c5cdfad5840a486e2fd0da67f08a5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/7/a830b4acff63b7d4110014621eabe025/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/4/c1714f6acc5d7a0bc9bb829fa7aaa4ac/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9hcy1pbnRlcm5hdGlvbmFsLTEyMzMxMi5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Poste de Travail H/F</t>
+          <t>Ingénieur·e Poste de Travail Windows H/F</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/8/561c978cab34ae54c8359c99c0cb8547/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc4NTU0NTg4Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09Nzg1NTQ1ODgmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/5/4c061858c84ea2ef8fcf32103b44b2e4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/10/f90826687cef2c02b253c584647f3f6e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc4NTU0NTg4Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09Nzg1NTQ1ODgmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/7/a830b4acff63b7d4110014621eabe025/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDE3MDk2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMTcwOTYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/11/f04a94fad4d56f10907714ebd7508c03/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/8/561c978cab34ae54c8359c99c0cb8547/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc4NTU0NTg4Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09Nzg1NTQ1ODgmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/13/aef97b224b6174726b096edef3514530/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/10/f90826687cef2c02b253c584647f3f6e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc4NTU0NTg4Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09Nzg1NTQ1ODgmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Ingénieur Poste de Travail H/F</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/26/8c2170634ed753dae089f555018987d5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/11/f04a94fad4d56f10907714ebd7508c03/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/27/5946f0abca4e1e21352e330b2f4b4c1a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/13/aef97b224b6174726b096edef3514530/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcxNTQ5NTY1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzE1NDk1NjUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -2256,22 +2256,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 07:39</t>
+          <t>2026-09-10 11:43</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur·e Outils Automation &amp; DevOps Si Industriel H/F</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Alert &lt;alerte@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/3/023a16d2481e1fed0182657124ffab5d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDI1MzA4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAyNTMwOCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/26/8c2170634ed753dae089f555018987d5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -2279,22 +2279,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 07:39</t>
+          <t>2026-09-10 11:43</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Alert &lt;alerte@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/5/3da60ac239d782e3ff904cb30c72d93f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDI1MzA4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAyNTMwOCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/b21aa583-8ce4-48b6-b491-add7ff4f3b73/27/5946f0abca4e1e21352e330b2f4b4c1a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Aws - Terraform - Full Remote H/F</t>
+          <t>Ingénieur·e Outils Automation &amp; DevOps Si Industriel H/F</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/6/c1edda81b0b7fff2a3b49c2897dccc12/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQxODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0MTg2MSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/3/023a16d2481e1fed0182657124ffab5d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDI1MzA4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAyNTMwOCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/8/05a9370a31b7a54f21dd2db56e5c6b93/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQxODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0MTg2MSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/5/3da60ac239d782e3ff904cb30c72d93f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDI1MzA4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAyNTMwOCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Sre Engineering Platform DevOps H/F</t>
+          <t>DevOps Engineer - Aws - Terraform - Full Remote H/F</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/9/884c0f4a1c049df22b9798b274889bf8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM2NTQ3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNjU0NyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/6/c1edda81b0b7fff2a3b49c2897dccc12/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQxODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0MTg2MSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/11/20b8db00bf811e8e7fadcd1f795e2261/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM2NTQ3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNjU0NyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/8/05a9370a31b7a54f21dd2db56e5c6b93/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQxODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0MTg2MSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur DevOps H/F</t>
+          <t>Sre Engineering Platform DevOps H/F</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/12/dc9cddbfb412532ee53c109263cc7b39/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2NDY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjQ2NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/9/884c0f4a1c049df22b9798b274889bf8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM2NTQ3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNjU0NyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/14/368148f5766230649c7bcf473f18e42b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2NDY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjQ2NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/11/20b8db00bf811e8e7fadcd1f795e2261/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM2NTQ3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNjU0NyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/15/1cb766da1baadec038beb2c103e50bd3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDE5OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAxOTk4MiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/12/dc9cddbfb412532ee53c109263cc7b39/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2NDY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjQ2NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/17/418f5dcffc3a9e6c6ce5a8349331a9fb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDE5OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAxOTk4MiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/14/368148f5766230649c7bcf473f18e42b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2NDY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjQ2NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Sre DevOps IA - Ml H/F</t>
+          <t>Ingénieur DevOps H/F</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/18/0fcabe154cfd5538f7e3549ccde7c422/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM1MTE3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNTExNyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/15/1cb766da1baadec038beb2c103e50bd3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDE5OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAxOTk4MiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/20/0a7f315676ef04f1b0f9604a06c180ed/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM1MTE3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNTExNyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/17/418f5dcffc3a9e6c6ce5a8349331a9fb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDE5OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MDAxOTk4MiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur DevOps H/F</t>
+          <t>Sre DevOps IA - Ml H/F</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/21/6d498138c9eab9c3c6ed01f7dd26ce87/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYzNzY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2Mzc2NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/18/0fcabe154cfd5538f7e3549ccde7c422/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM1MTE3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNTExNyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/23/181f280baeff9e2efdc4923cccd03e31/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYzNzY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2Mzc2NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/20/0a7f315676ef04f1b0f9604a06c180ed/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM1MTE3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzNTExNyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/24/1e1aabc6f5d0daffb25cceaecda815a6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYxODY3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2MTg2NyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/21/6d498138c9eab9c3c6ed01f7dd26ce87/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYzNzY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2Mzc2NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/26/daf345958416eb73bb7083e07f7a80a5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYxODY3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2MTg2NyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/23/181f280baeff9e2efdc4923cccd03e31/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYzNzY0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2Mzc2NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>DevOps - Editeur de Logiciel Deeptech &amp; IA H/F</t>
+          <t>Ingénieur DevOps H/F</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/27/24b125ff906103c2812b588f475f70cd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU4NDU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk1ODQ1NSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/24/1e1aabc6f5d0daffb25cceaecda815a6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYxODY3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2MTg2NyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/29/51659695aedc34d71d87c4a6d26fd595/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU4NDU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk1ODQ1NSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/26/daf345958416eb73bb7083e07f7a80a5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTYxODY3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk2MTg2NyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Ingenieur Devsecops H/F</t>
+          <t>DevOps - Editeur de Logiciel Deeptech &amp; IA H/F</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/30/e712def15fd734ddbc12b60158070472/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQwMzk3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0MDM5NyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/27/24b125ff906103c2812b588f475f70cd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU4NDU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk1ODQ1NSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/32/42ee46708bed661e15d6a69c9c0e27a6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQwMzk3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0MDM5NyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/29/51659695aedc34d71d87c4a6d26fd595/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU4NDU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk1ODQ1NSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Confirmé DevOps H/F</t>
+          <t>Ingenieur Devsecops H/F</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/33/7bb74a33f37bf874f1672658325638d2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ1NjU0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NTY1NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/30/e712def15fd734ddbc12b60158070472/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQwMzk3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0MDM5NyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/35/c42a33da8356985ed02f53ed9f80dd70/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ1NjU0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NTY1NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/32/42ee46708bed661e15d6a69c9c0e27a6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQwMzk3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0MDM5NyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Architecte DevOps H/F</t>
+          <t>Ingénieur Confirmé DevOps H/F</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/36/e5783ad821ab5873ec9b765b148a8a7b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc4MDM2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3ODAzNiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/33/7bb74a33f37bf874f1672658325638d2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ1NjU0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NTY1NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/38/13845b30d05a426c0b10d9926dbb5871/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc4MDM2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3ODAzNiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/35/c42a33da8356985ed02f53ed9f80dd70/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ1NjU0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NTY1NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Consultant ou Architecte DevOps ou Cloud Gcp H/F</t>
+          <t>Architecte DevOps H/F</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/39/72dab0efdd6a0a2d3bc24d64823ebcff/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjI5NTE1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIyOTUxNSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/36/e5783ad821ab5873ec9b765b148a8a7b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc4MDM2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3ODAzNiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/41/abea5e648e7f563cb2707ae4b131a23f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjI5NTE1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIyOTUxNSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/38/13845b30d05a426c0b10d9926dbb5871/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc4MDM2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3ODAzNiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Teach Lead DevOps H/F</t>
+          <t>Consultant ou Architecte DevOps ou Cloud Gcp H/F</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/42/6a124964437b0b3c28bea3b5ac2a8670/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUyNDQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MjQ0MCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/39/72dab0efdd6a0a2d3bc24d64823ebcff/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjI5NTE1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIyOTUxNSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/44/7d4e5ca1bb06017e316efcb038a2bb6f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUyNDQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MjQ0MCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/41/abea5e648e7f563cb2707ae4b131a23f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjI5NTE1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIyOTUxNSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Développeur DevOps - Backend H/F</t>
+          <t>Teach Lead DevOps H/F</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/45/e4145199ed96737b71036577b296c506/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUwMTMwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MDEzMCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/42/6a124964437b0b3c28bea3b5ac2a8670/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUyNDQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MjQ0MCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/47/9daa6222ff0cf001271df4564c6b2c9d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUwMTMwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MDEzMCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/44/7d4e5ca1bb06017e316efcb038a2bb6f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUyNDQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MjQ0MCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>DevOps Project Manager H/F</t>
+          <t>Développeur DevOps - Backend H/F</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/48/397e546269fa45a977139f1a6acdf68f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3NzU5NjYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc1OTY2MSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/45/e4145199ed96737b71036577b296c506/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUwMTMwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MDEzMCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/50/e517e9a37db1a320ab2c255a279210e0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3NzU5NjYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc1OTY2MSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/47/9daa6222ff0cf001271df4564c6b2c9d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUwMTMwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1MDEzMCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer H/F</t>
+          <t>DevOps Project Manager H/F</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/51/2684da8ab3246fcd4565b88fdb88ae7a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc1ODEzLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3NTgxMyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/48/397e546269fa45a977139f1a6acdf68f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3NzU5NjYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc1OTY2MSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/53/20b941dbcaa3f1064ab4e470940c3f5f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc1ODEzLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3NTgxMyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/50/e517e9a37db1a320ab2c255a279210e0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3NzU5NjYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc1OTY2MSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur DevOps - Devsecops Senior H/F</t>
+          <t>Senior DevOps Engineer H/F</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/54/6e206dc028d80dfedd65c9ce69d37a46/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODUyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1MiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/51/2684da8ab3246fcd4565b88fdb88ae7a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc1ODEzLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3NTgxMyZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/56/c90626cbbc2b4c02a78c2d24e8284d22/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODUyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1MiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/53/20b941dbcaa3f1064ab4e470940c3f5f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzc3Nzc1ODEzLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT03Nzc3NTgxMyZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>DevOps Fullstack H/F</t>
+          <t>Ingénieur DevOps - Devsecops Senior H/F</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/57/0450eaa8bce8e4fa6c1cab0337c654cf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1NSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/54/6e206dc028d80dfedd65c9ce69d37a46/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODUyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1MiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/59/9773dd4c6cc6be8812b9d38bbe2018ec/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1NSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/56/c90626cbbc2b4c02a78c2d24e8284d22/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODUyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1MiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur DevOps H/F</t>
+          <t>DevOps Fullstack H/F</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/62/029af576d5dd69ce8008ab1c17985a07/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzk2MTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5NjEwNyZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/57/0450eaa8bce8e4fa6c1cab0337c654cf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1NSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/64/2de12e88453e55d70a437f994adfcccd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzk2MTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5NjEwNyZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/59/9773dd4c6cc6be8812b9d38bbe2018ec/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwODU1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDg1NSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur DevOps Cloud Sre - Secteur de la Santé H/F</t>
+          <t>Ingénieur DevOps H/F</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/65/b950d6932caa1c388c6527be120876b2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA1OTQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNTk0MCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/62/029af576d5dd69ce8008ab1c17985a07/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzk2MTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5NjEwNyZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/67/b90b59e8b7c2b4422677b7f1abff11bb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA1OTQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNTk0MCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/64/2de12e88453e55d70a437f994adfcccd/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzk2MTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5NjEwNyZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Consultant Développement DevOps - Craftmanship H/F</t>
+          <t>Ingénieur DevOps Cloud Sre - Secteur de la Santé H/F</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/68/f0f613447d4c55fb748949a0804546c1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDg1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ4NSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/65/b950d6932caa1c388c6527be120876b2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA1OTQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNTk0MCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/70/d5a3c7e7610a8cae5c8ff8caa07796f8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDg1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ4NSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/67/b90b59e8b7c2b4422677b7f1abff11bb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA1OTQwLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNTk0MCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Consultant Devsecops Senior H/F</t>
+          <t>Consultant Développement DevOps - Craftmanship H/F</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/71/ebe94ff82aeafb9315389a494de7320f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDk2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5NiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/68/f0f613447d4c55fb748949a0804546c1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDg1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ4NSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/73/fd2a12fb7eabb6758908c98e98fd4869/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDk2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5NiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/70/d5a3c7e7610a8cae5c8ff8caa07796f8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDg1Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ4NSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Ingenieur DevOps Expert Kubernetes - Agence Tech H/F</t>
+          <t>Consultant Devsecops Senior H/F</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/74/f3c860ad412c7eeceda556bc9a8f072c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjE2MjUxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYxNjI1MSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/71/ebe94ff82aeafb9315389a494de7320f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDk2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5NiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/76/fa8a51dd1e3f24b37b632935b4a8c496/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjE2MjUxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYxNjI1MSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/73/fd2a12fb7eabb6758908c98e98fd4869/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDk2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5NiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Ingénieur Devsecops - Cloud H/F</t>
+          <t>Ingenieur DevOps Expert Kubernetes - Agence Tech H/F</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/77/5174eea10e91030bd9a38905e87d6867/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjIyNjU5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYyMjY1OSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/74/f3c860ad412c7eeceda556bc9a8f072c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjE2MjUxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYxNjI1MSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/79/c705766711b71c8d329d0de72b29c2cc/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjIyNjU5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYyMjY1OSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/76/fa8a51dd1e3f24b37b632935b4a8c496/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjE2MjUxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYxNjI1MSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Manager DevOps H/F</t>
+          <t>Ingénieur Devsecops - Cloud H/F</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/80/6caba3753f462247f9f957c11f453980/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjU5NTczLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY1OTU3MyZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/77/5174eea10e91030bd9a38905e87d6867/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjIyNjU5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYyMjY1OSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/82/84809b8a0846eb76be2e66898e92db35/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjU5NTczLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY1OTU3MyZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/79/c705766711b71c8d329d0de72b29c2cc/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjIyNjU5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjYyMjY1OSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Sre Senior - Lead Platform Engineer H/F</t>
+          <t>Manager DevOps H/F</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/83/2adcc129a07e18021a383c99da33989d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjYwOTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY2MDkwNyZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/80/6caba3753f462247f9f957c11f453980/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjU5NTczLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY1OTU3MyZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/85/116ede087dacf585eb4f1c0bb40ed00a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjYwOTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY2MDkwNyZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/82/84809b8a0846eb76be2e66898e92db35/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjU5NTczLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY1OTU3MyZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Sre Senior - Lead Platform Engineer H/F</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/98/d94408778af5b9565507e89fde25ae49/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydA</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/83/2adcc129a07e18021a383c99da33989d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjYwOTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY2MDkwNyZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/99/ceec1e4b8aa5360dbe8c407b66eebb41/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPWpvYmFsZXJ0JnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWpvYmFsZXJ0JnV0bV9jb250ZW50PWNvbnRhY3Q</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/85/116ede087dacf585eb4f1c0bb40ed00a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNjYwOTA3Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjY2MDkwNyZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>vos préférences</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/102/8f93deeea4ef491f2c7583ac21a7032d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tZXMtYWxlcnRlcy5odG1sP3V0bV9zb3VyY2U9am9iYWxlcnQmdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249am9iYWxlcnQmdXRtX2NvbnRlbnQ9cHJlZmVyZW5jZXM</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/98/d94408778af5b9565507e89fde25ae49/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydA</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Administrateur Systèmes Linux H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/3/126d5df3e01b161cbf462d45fea4158a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0Njk4MiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/99/ceec1e4b8aa5360dbe8c407b66eebb41/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPWpvYmFsZXJ0JnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWpvYmFsZXJ0JnV0bV9jb250ZW50PWNvbnRhY3Q</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>vos préférences</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/5/51cf25e71f129dce4bd117df0b837580/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0Njk4MiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/10f5ef05-3fdd-4b80-aeb8-2ecbb2b6a220/102/8f93deeea4ef491f2c7583ac21a7032d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tZXMtYWxlcnRlcy5odG1sP3V0bV9zb3VyY2U9am9iYWxlcnQmdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249am9iYWxlcnQmdXRtX2NvbnRlbnQ9cHJlZmVyZW5jZXM</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Administrateur Système Linux H/F</t>
+          <t>Administrateur Systèmes Linux H/F</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/8/66e22162f1eaf37d2327a06a2b996a8b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTMyOTk0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjkzMjk5NCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/3/126d5df3e01b161cbf462d45fea4158a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0Njk4MiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/10/5c245c378023788ad0c3c43845d64ac6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTMyOTk0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjkzMjk5NCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/5/51cf25e71f129dce4bd117df0b837580/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2OTgyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0Njk4MiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Administrateur Systèmes Linux H/F</t>
+          <t>Administrateur Système Linux H/F</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/11/01d52ff55f5ca027ee3628b88662f09a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMTg4MTY2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzE4ODE2NiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/8/66e22162f1eaf37d2327a06a2b996a8b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTMyOTk0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjkzMjk5NCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/13/0f0017371890910333b19f6c75d955e1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMTg4MTY2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzE4ODE2NiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/10/5c245c378023788ad0c3c43845d64ac6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTMyOTk0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjkzMjk5NCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Administrateur Système Linux H/F</t>
+          <t>Administrateur Systèmes Linux H/F</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/14/8a7e527aad6d421a9c9398e0b2b1a168/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMDkwNzgxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzA5MDc4MSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/11/01d52ff55f5ca027ee3628b88662f09a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMTg4MTY2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzE4ODE2NiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/16/e1b35f4148d0a204f3dd62edd62ba824/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMDkwNzgxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzA5MDc4MSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/13/0f0017371890910333b19f6c75d955e1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMTg4MTY2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzE4ODE2NiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Administrateur Système Linux H/F</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/29/f25e07ae5bb9caebb4f9ef7ac863a728/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydA</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/14/8a7e527aad6d421a9c9398e0b2b1a168/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMDkwNzgxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzA5MDc4MSZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/30/45a7237600936725fb3414829f58317f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPWpvYmFsZXJ0JnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWpvYmFsZXJ0JnV0bV9jb250ZW50PWNvbnRhY3Q</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/16/e1b35f4148d0a204f3dd62edd62ba824/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMDkwNzgxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MzA5MDc4MSZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>vos préférences</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/33/b6ee67d130223500c011da579674cd84/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tZXMtYWxlcnRlcy5odG1sP3V0bV9zb3VyY2U9am9iYWxlcnQmdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249am9iYWxlcnQmdXRtX2NvbnRlbnQ9cHJlZmVyZW5jZXM</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/29/f25e07ae5bb9caebb4f9ef7ac863a728/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydA</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Développeur Full-Stack Remédiation &amp; Dette Technique H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/3/9f21732196824c99b67a2363834eaa17/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2Mzg0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjM4NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/30/45a7237600936725fb3414829f58317f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPWpvYmFsZXJ0JnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWpvYmFsZXJ0JnV0bV9jb250ZW50PWNvbnRhY3Q</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>vos préférences</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/5/9111059f3d9ffafd5d1dd178afc4b28a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2Mzg0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjM4NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/7c6908ef-e38b-411f-81bc-7635373cf351/33/b6ee67d130223500c011da579674cd84/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tZXMtYWxlcnRlcy5odG1sP3V0bV9zb3VyY2U9am9iYWxlcnQmdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249am9iYWxlcnQmdXRtX2NvbnRlbnQ9cHJlZmVyZW5jZXM</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Full Stack .Net - React.Js H/F</t>
+          <t>Développeur Full-Stack Remédiation &amp; Dette Technique H/F</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/6/40b1fc9f73232c7276396ce39dc59cbe/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjcwNzQ5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI3MDc0OSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/3/9f21732196824c99b67a2363834eaa17/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2Mzg0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjM4NCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/8/a77db1afaf15c1698b71807b654c61e7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjcwNzQ5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI3MDc0OSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/5/9111059f3d9ffafd5d1dd178afc4b28a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjQ2Mzg0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI0NjM4NCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer H/F</t>
+          <t>Tech Lead Full Stack .Net - React.Js H/F</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/9/7034cdfc91a3fa49b5144861bbabd476/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQ3Nzg2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0Nzc4NiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/6/40b1fc9f73232c7276396ce39dc59cbe/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjcwNzQ5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI3MDc0OSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/11/d99e8439af21c2d0d1fca36e82938a3f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQ3Nzg2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0Nzc4NiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/8/a77db1afaf15c1698b71807b654c61e7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjcwNzQ5Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI3MDc0OSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Développeur Fullstack Confirmé H/F</t>
+          <t>Fullstack Developer H/F</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/12/ce0106ed3b15bf0617d3db5edfc7d981/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYzOTcxODY4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT02Mzk3MTg2OCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/9/7034cdfc91a3fa49b5144861bbabd476/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQ3Nzg2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0Nzc4NiZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/14/1e4f68fdadf782e5c9d1e8a3bd242d62/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYzOTcxODY4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT02Mzk3MTg2OCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/11/d99e8439af21c2d0d1fca36e82938a3f/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTQ3Nzg2Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04Mjk0Nzc4NiZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Fullstack Developer H/F</t>
+          <t>Développeur Fullstack Confirmé H/F</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/15/91f18581c9a15551cda112ae39913169/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM4MDM0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzODAzNCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/12/ce0106ed3b15bf0617d3db5edfc7d981/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYzOTcxODY4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT02Mzk3MTg2OCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/17/a815e69a0b772ee0fe2e865e36d0faff/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM4MDM0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzODAzNCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/14/1e4f68fdadf782e5c9d1e8a3bd242d62/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYzOTcxODY4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT02Mzk3MTg2OCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Développeur Full Stack H/F</t>
+          <t>Fullstack Developer H/F</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/18/0c895b8b1122794a345263d6f6b30a93/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUzODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1Mzg2MSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/15/91f18581c9a15551cda112ae39913169/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM4MDM0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzODAzNCZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/20/92ca2c008fc177943b30ff202df1b32a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUzODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1Mzg2MSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/17/a815e69a0b772ee0fe2e865e36d0faff/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjM4MDM0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzODAzNCZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Développeur Full Stack Confirmé .Net - Angular H/F</t>
+          <t>Développeur Full Stack H/F</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/21/0162ae485adc4e0163ea7986ad45c8cf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwOTExLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDkxMSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/18/0c895b8b1122794a345263d6f6b30a93/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUzODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1Mzg2MSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/23/c4d576e33f713b95cdf3363d8011c227/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwOTExLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDkxMSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/20/92ca2c008fc177943b30ff202df1b32a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjUzODYxLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzI1Mzg2MSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Développeur·se Full Stack Mobile React Native - Node.Js Expert H/F</t>
+          <t>Développeur Full Stack Confirmé .Net - Angular H/F</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/26/6a5bbc49bee391c7c3bbc78046e19dd9/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA2MDA0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNjAwNCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/21/0162ae485adc4e0163ea7986ad45c8cf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwOTExLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDkxMSZ1dG1fY29udGVudD1vZmZyZV90aXRsZQ</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/28/e686e5e5fabfd818c9af11341efb0ed8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA2MDA0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNjAwNCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/23/c4d576e33f713b95cdf3363d8011c227/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgzMjMwOTExLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydCZ1dG1fdGVybT04MzIzMDkxMSZ1dG1fY29udGVudD1saXN0ZTFDVEE</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Chef de Projet Développeur Full Stack H/F</t>
+          <t>Développeur·se Full Stack Mobile React Native - Node.Js Expert H/F</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/29/782958e5d3eae361a2d6184206a6cec2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5MDUyNCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/26/6a5bbc49bee391c7c3bbc78046e19dd9/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA2MDA0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNjAwNCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/31/f7e8dafac14e50e0b10f189fb2522a33/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5MDUyNCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/28/e686e5e5fabfd818c9af11341efb0ed8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODA2MDA0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwNjAwNCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Développeur Fullstack Senior - Lead Engineer - CDI H/F</t>
+          <t>Chef de Projet Développeur Full Stack H/F</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/32/b4dda37316be76d41c7e6d6bb01153bf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODE0NDk4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgxNDQ5OCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/29/782958e5d3eae361a2d6184206a6cec2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5MDUyNCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/34/6b0ad93e55aaf7fbab2fa678864934df/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODE0NDk4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgxNDQ5OCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/31/f7e8dafac14e50e0b10f189fb2522a33/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04Mjc5MDUyNCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Consultant Fullstack C# H/F</t>
+          <t>Développeur Fullstack Senior - Lead Engineer - CDI H/F</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/35/6271ea3f007dd540cf6cb8e44e26a515/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDkyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5MiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/32/b4dda37316be76d41c7e6d6bb01153bf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODE0NDk4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgxNDQ5OCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/37/8b12cd0dc0406a41d386fc6506e941c7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDkyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5MiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/34/6b0ad93e55aaf7fbab2fa678864934df/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODE0NDk4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgxNDQ5OCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Développeur Full Stack React - Next.Js - Golang - Node - Poste Hybride Dev H/F</t>
+          <t>Consultant Fullstack C# H/F</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/38/1ca79bdb281f6a92e3fa3e497678cddf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxODkyNDM4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MTg5MjQzOCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/35/6271ea3f007dd540cf6cb8e44e26a515/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDkyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5MiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/40/4f97538adf61c766041f32083d64b681/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxODkyNDM4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MTg5MjQzOCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/37/8b12cd0dc0406a41d386fc6506e941c7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAwNDkyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MjgwMDQ5MiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Développeur Fullstack Kotlin - React H/F</t>
+          <t>Développeur Full Stack React - Next.Js - Golang - Node - Poste Hybride Dev H/F</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/41/b5af105c737c7bc17ceb612f12928068/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYwOTQ1NTcyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT02MDk0NTU3MiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/38/1ca79bdb281f6a92e3fa3e497678cddf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxODkyNDM4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MTg5MjQzOCZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/43/7dd24d2691abc64e0e602314a1068f70/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYwOTQ1NTcyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT02MDk0NTU3MiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/40/4f97538adf61c766041f32083d64b681/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxODkyNDM4Lmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT04MTg5MjQzOCZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Développeur Fullstack Kotlin - React H/F</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/56/33ed37a0717ec7d38bc6bdba1ab4b233/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydA</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/41/b5af105c737c7bc17ceb612f12928068/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYwOTQ1NTcyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT02MDk0NTU3MiZ1dG1fY29udGVudD1saXN0ZTJ0aXRsZQ</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/57/d0cbd43901baa72af998e384241290ac/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPWpvYmFsZXJ0JnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWpvYmFsZXJ0JnV0bV9jb250ZW50PWNvbnRhY3Q</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/43/7dd24d2691abc64e0e602314a1068f70/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzYwOTQ1NTcyLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydF9jb25uZXhlcyZ1dG1fdGVybT02MDk0NTU3MiZ1dG1fY29udGVudD1saXN0ZTJDVEE</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>vos préférences</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/60/95e46000c7cde2176d3d93f5bf5f2916/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tZXMtYWxlcnRlcy5odG1sP3V0bV9zb3VyY2U9am9iYWxlcnQmdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249am9iYWxlcnQmdXRtX2NvbnRlbnQ9cHJlZmVyZW5jZXM</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/56/33ed37a0717ec7d38bc6bdba1ab4b233/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1qb2JhbGVydCZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1qb2JhbGVydA</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -4492,17 +4492,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Voir l'emploi</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
+          <t>Alerte email — Hellowork Alert &lt;alerte@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32TWaurWBBG_0ug89Te4xCHfSA0jtHEMZoY8yK61Wict5poLve_X7tp-rGhoGB9RVH1sH5ups33Jh_Hbvj--srQj6JJ0jT5Adv6q4seaZR8war8K0NtvX-2cUFG4dqGdkIwRViGMOUcpnVUVNu63aNtlOwxxgyqOCtNnKf71swIdcrLAjznM-Ysqty8UnFiz28dfgDDn3RwNhZW0uEV49vQvE5aJBlzeImX_nPpxOts4bANROqjYp54ORKkXxEeDr3BPi4zc44y3d0V7AvXh7ebkgsCurQMD5rmqaNwdJTL-0WTpUJOlzios4tKXqjCyxYut2t2ejf0boRdZeEWW-6Y2sjojjhMDzQgPoU2ptz8IGJcAAnyGXgwWqzkzFL51YdBLdM6fbjliVKE0L3fHt0HJ2-VKAmSFIGIovGPSKYiUib_qhGCUg936_Sc25bTBUCSza07t9bRC2g0OI71NsR7HE69oVBWMdFKDc5cXQq3jl4g0RmlMFhunT9R5Z4qVNDxHGpTE8mHo6JCOs0cMse6kE2MyWQ-6ngRmaEyXk1F8QwgkSunaggSnrm58N2lCM1H2X83bu_ZqvJyHq43lCUSaGeUR8FnYtJzDlJ9CEHPnmIbSTljze9Mcyz8Lj3C3BTBKV_qwnPGtycyueI28o70C2ZQQiCK_d3kbaLPRjGyRq0QZCd2e5Fr_GcQl9mdm81X27iChum069c8Gezm0bUFLZVxxN8wz7m0EQcl8RhYvpugeqcjvooPEu1VShCAdMqCcyImmd_7WqXk4vVmUfFusQ1Fc16meeCszGLJfrI9bayV_K45eGPpBKleB8W9ephbdrF5VWkr2WW22sfWSCwNg6SwxMxQ_ohQBPAlrU9eT6d0QQZlJDW70CSyLoJKa6Gc6iClD27SOoYVSLV5vFrJnPJ_UNJaW1Tvye1cwnjvtiLFhAaZHmLSb2_wc8df8adcb7ft7XOI9izYMVsY1eVepGTb_SiV8wbq8mm16XWc_H83bv7c1Jvvn5sIwnZqRi1Zbd0BwFEcDpg1jB6PYxv_gwFgaQanGI5bOawKWHo5aqdHvmYjmtL_6NKlK3oV6XtVeaV_y72C_9V7HRvLdYgoSQZM8TgWzw5yOLH59es3E4B2TUMEAAA/CbipPTpLjFUDxzTiE3FVjlpdZOkIMgy3686G3TRItow</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/57/d0cbd43901baa72af998e384241290ac/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPWpvYmFsZXJ0JnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWpvYmFsZXJ0JnV0bV9jb250ZW50PWNvbnRhY3Q</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -4515,17 +4515,17 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Ne correspond pas</t>
+          <t>vos préférences</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
+          <t>Alerte email — Hellowork Alert &lt;alerte@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QwW6jMBRF_wVpZjVuoMQEIlWjJm0IIYhASFp1UxljwAFsYmzSpOq_j6eLWczbXOncKz3pfBrKmBu1lP0wn0w6JHF9R1lBSHGHeTehbKQSScrZMGFcAsokEWSQpPgtmweruXc8lUtJTz12TesnZSV_ePx7h-OiyosTYDcZxMyn03W6eopCgZIq2rJrM_vIfEgDML29fbzG_nlVwWOcxOkm2vXlYdHalguHA3RAospXyCC5JmuWHM9-ulRSwHJpF3sTb5sqiMQIffZ8cRbEPF8fEyr3a0LOWbgN7OV2DMd0P7bZzCrTaXZsXJCZyWix3e6WOC9pS0Nm-xf01r2EYdUpBDZ9GFu3dVdHz-zyw34yfhmdMf80EMZcMRkUWtfU81zbNT1Hl6iqNjz_xp43g45pO66rOW4pbrJacFXVupNCkX_02hONclSAb-Gal4LrL8aJ5_QevesYuBKYCFAKsErfSYdoq2ey0aP_rRtfX38ArET9UsYBAAA/1VVYqz2XVOt1mM6E2Gr--hvrD8_3q1ustLIuW8IQ4wo</t>
+          <t>https://emails.hellowork.com/clic/38e92633-4113-4779-9923-c4a0357c4ca6/60/95e46000c7cde2176d3d93f5bf5f2916/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tZXMtYWxlcnRlcy5odG1sP3V0bV9zb3VyY2U9am9iYWxlcnQmdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249am9iYWxlcnQmdXRtX2NvbnRlbnQ9cHJlZmVyZW5jZXM</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Modifier le profil</t>
+          <t>Voir l'emploi</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OMQuDMBSE_0sGp0arLWIE6SZ0le4Sn0kTNUaeL0MR_3szlE4Hdx93d7DAamaItr3Osg29totK7ToqNabg3UOjd83kB1vIPsruA4JCrpG3Xa-ctEsCvmm7xCyNRnZhjtUHkwA-rPQcY_ldiOpWXUUZQ1gszC-DPrxNjAiD-rufTUVrdxKJ6zg_SJi5Gi3x361I0hyRfC5KEQYiO21QXXN2nl8frfmaxwAAAA/8XK_unsabwbO2ZltIzfCXINrDK_l5BNkxL6pMXg3tY4</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32TWaurWBBG_0ug89Te4xCHfSA0jtHEMZoY8yK61Wict5poLve_X7tp-rGhoGB9RVH1sH5ups33Jh_Hbvj--srQj6JJ0jT5Adv6q4seaZR8war8K0NtvX-2cUFG4dqGdkIwRViGMOUcpnVUVNu63aNtlOwxxgyqOCtNnKf71swIdcrLAjznM-Ysqty8UnFiz28dfgDDn3RwNhZW0uEV49vQvE5aJBlzeImX_nPpxOts4bANROqjYp54ORKkXxEeDr3BPi4zc44y3d0V7AvXh7ebkgsCurQMD5rmqaNwdJTL-0WTpUJOlzios4tKXqjCyxYut2t2ejf0boRdZeEWW-6Y2sjojjhMDzQgPoU2ptz8IGJcAAnyGXgwWqzkzFL51YdBLdM6fbjliVKE0L3fHt0HJ2-VKAmSFIGIovGPSKYiUib_qhGCUg936_Sc25bTBUCSza07t9bRC2g0OI71NsR7HE69oVBWMdFKDc5cXQq3jl4g0RmlMFhunT9R5Z4qVNDxHGpTE8mHo6JCOs0cMse6kE2MyWQ-6ngRmaEyXk1F8QwgkSunaggSnrm58N2lCM1H2X83bu_ZqvJyHq43lCUSaGeUR8FnYtJzDlJ9CEHPnmIbSTljze9Mcyz8Lj3C3BTBKV_qwnPGtycyueI28o70C2ZQQiCK_d3kbaLPRjGyRq0QZCd2e5Fr_GcQl9mdm81X27iChum069c8Gezm0bUFLZVxxN8wz7m0EQcl8RhYvpugeqcjvooPEu1VShCAdMqCcyImmd_7WqXk4vVmUfFusQ1Fc16meeCszGLJfrI9bayV_K45eGPpBKleB8W9ephbdrF5VWkr2WW22sfWSCwNg6SwxMxQ_ohQBPAlrU9eT6d0QQZlJDW70CSyLoJKa6Gc6iClD27SOoYVSLV5vFrJnPJ_UNJaW1Tvye1cwnjvtiLFhAaZHmLSb2_wc8df8adcb7ft7XOI9izYMVsY1eVepGTb_SiV8wbq8mm16XWc_H83bv7c1Jvvn5sIwnZqRi1Zbd0BwFEcDpg1jB6PYxv_gwFgaQanGI5bOawKWHo5aqdHvmYjmtL_6NKlK3oV6XtVeaV_y72C_9V7HRvLdYgoSQZM8TgWzw5yOLH59es3E4B2TUMEAAA/CbipPTpLjFUDxzTiE3FVjlpdZOkIMgy3686G3TRItow</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Suspendre ces emails</t>
+          <t>Ne correspond pas</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qy26CQABF_4WkXRWB8hBMTOMTEAiCiMYdwgAjMLxmUDD-e2kXXfTu7jm786QINaNSjKt2xjBFgMN0AlEEQDQJy4KBqIM4wLBELVMFpAVfOJtz2aekkCvG8FaFMsu9QxSX88XPjv4yuUY3Gg1Yt5EKBc3dri2jCZzEMlGfTR-eKkKdFobL42yr9TYRfdux3Z21r-LjMuc5WWyPokQ7JD6LSAS9oyHHr1V3RXAjxis-OrChmSW61XSiijZ3aQnYul84EB80AGrPMHV-ZXZG5x663JtysSt4fibTHut0HNrvB0c6uTk0EK_eg0txMoykIAG9qwybG7QitTbo_savqQ-qoGZPKgjDkiCsR2MlQVFkXmYVaZRhDsPMS5uSJOmocEPAH-0rMKLfXCPD2Xj-J6Ner28nBiyAegEAAA/YRVbf1NzlRaIBdx58efQiQzYp7bQzK3eaPtFGrlgQyg</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QwW6jMBRF_wVpZjVuoMQEIlWjJm0IIYhASFp1UxljwAFsYmzSpOq_j6eLWczbXOncKz3pfBrKmBu1lP0wn0w6JHF9R1lBSHGHeTehbKQSScrZMGFcAsokEWSQpPgtmweruXc8lUtJTz12TesnZSV_ePx7h-OiyosTYDcZxMyn03W6eopCgZIq2rJrM_vIfEgDML29fbzG_nlVwWOcxOkm2vXlYdHalguHA3RAospXyCC5JmuWHM9-ulRSwHJpF3sTb5sqiMQIffZ8cRbEPF8fEyr3a0LOWbgN7OV2DMd0P7bZzCrTaXZsXJCZyWix3e6WOC9pS0Nm-xf01r2EYdUpBDZ9GFu3dVdHz-zyw34yfhmdMf80EMZcMRkUWtfU81zbNT1Hl6iqNjz_xp43g45pO66rOW4pbrJacFXVupNCkX_02hONclSAb-Gal4LrL8aJ5_QevesYuBKYCFAKsErfSYdoq2ey0aP_rRtfX38ArET9UsYBAAA/1VVYqz2XVOt1mM6E2Gr--hvrD8_3q1ustLIuW8IQ4wo</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Centre d'aide</t>
+          <t>Modifier le profil</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ6CMBBF7zJrQ0ENaZsY1-69gEyLrQXalJkFIdzdWRiX_728vwODhUBUVqvUyqXkSk1cnPeuwTyrgGqs9zDdxgonmMHu8ELMvNDDSXk1Rl90a3qROEVMz1Azv4Moquz_dCte0O9fKCWZXTr3hgei-Cmo2w6O4wtbuyGXkAAAAA/s2Xf8nxjFrGlZnkJ4azX-1qNKhXxoNvTTgZT4r6OQi4</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OMQuDMBSE_0sGp0arLWIE6SZ0le4Sn0kTNUaeL0MR_3szlE4Hdx93d7DAamaItr3Osg29totK7ToqNabg3UOjd83kB1vIPsruA4JCrpG3Xa-ctEsCvmm7xCyNRnZhjtUHkwA-rPQcY_ldiOpWXUUZQ1gszC-DPrxNjAiD-rufTUVrdxKJ6zg_SJi5Gi3x361I0hyRfC5KEQYiO21QXXN2nl8frfmaxwAAAA/8XK_unsabwbO2ZltIzfCXINrDK_l5BNkxL6pMXg3tY4</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Conditions d'utilisation</t>
+          <t>Suspendre ces emails</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ7CIBBF7zJuTWnVNEBiXLv3AnU6LQgUQoeFaXp36cblfy_vb1BAg2FOqxZiyo1dRqKxwRiEp3nwD-PvUz5xXOEMAfQGA2IsCz_HGt6UklfZqr5K9Bbdy-RYZlMV50J_-k10IMrhuGFXR-cuvSpvZvtJKNsO9v0HbfTICI0AAAA/80UsACYos9nQu1FFHc5kOO-FgMrYI30yN1QhY-oyBTE</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qy26CQABF_4WkXRWB8hBMTOMTEAiCiMYdwgAjMLxmUDD-e2kXXfTu7jm786QINaNSjKt2xjBFgMN0AlEEQDQJy4KBqIM4wLBELVMFpAVfOJtz2aekkCvG8FaFMsu9QxSX88XPjv4yuUY3Gg1Yt5EKBc3dri2jCZzEMlGfTR-eKkKdFobL42yr9TYRfdux3Z21r-LjMuc5WWyPokQ7JD6LSAS9oyHHr1V3RXAjxis-OrChmSW61XSiijZ3aQnYul84EB80AGrPMHV-ZXZG5x663JtysSt4fibTHut0HNrvB0c6uTk0EK_eg0txMoykIAG9qwybG7QitTbo_savqQ-qoGZPKgjDkiCsR2MlQVFkXmYVaZRhDsPMS5uSJOmocEPAH-0rMKLfXCPD2Xj-J6Ner28nBiyAegEAAA/YRVbf1NzlRaIBdx58efQiQzYp7bQzK3eaPtFGrlgQyg</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -4630,17 +4630,17 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Centre d'aide</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/4/e070c7f270d5b1027d157299cf01ca05/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy92aXZlcmlzLTEwNTU2NC5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ6CMBBF7zJrQ0ENaZsY1-69gEyLrQXalJkFIdzdWRiX_728vwODhUBUVqvUyqXkSk1cnPeuwTyrgGqs9zDdxgonmMHu8ELMvNDDSXk1Rl90a3qROEVMz1Azv4Moquz_dCte0O9fKCWZXTr3hgei-Cmo2w6O4wtbuyGXkAAAAA/s2Xf8nxjFrGlZnkJ4azX-1qNKhXxoNvTTgZT4r6OQi4</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
+          <t>Conditions d'utilisation</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/5/396bbbe70b896c89fc6377d7c2ecbd7c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ7CIBBF7zJuTWnVNEBiXLv3AnU6LQgUQoeFaXp36cblfy_vb1BAg2FOqxZiyo1dRqKxwRiEp3nwD-PvUz5xXOEMAfQGA2IsCz_HGt6UklfZqr5K9Bbdy-RYZlMV50J_-k10IMrhuGFXR-cuvSpvZvtJKNsO9v0HbfTICI0AAAA/80UsACYos9nQu1FFHc5kOO-FgMrYI30yN1QhY-oyBTE</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/7/1fcbc76835e28d4703f88d6999c1a195/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/4/e070c7f270d5b1027d157299cf01ca05/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy92aXZlcmlzLTEwNTU2NC5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Développeur Java - Aws H/F</t>
+          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/8/948de73f5fa50fdaea391f4eb188c2d7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/5/396bbbe70b896c89fc6377d7c2ecbd7c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/10/6f0fc39a6868014e74e6e37180b9d20e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/7/1fcbc76835e28d4703f88d6999c1a195/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
+          <t>Développeur Java - Aws H/F</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/11/62a227c11def9dffea63c2e948e31817/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/8/948de73f5fa50fdaea391f4eb188c2d7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/13/eb6ac004652fb9c2fc56a2ae8ec8a51b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/10/6f0fc39a6868014e74e6e37180b9d20e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Java - Angular H/F</t>
+          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/14/6ea4a8aadb72d35272d90eb698589b9a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/11/62a227c11def9dffea63c2e948e31817/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/16/7fa934aed9dd11309508bb5e4d7957cf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/13/eb6ac004652fb9c2fc56a2ae8ec8a51b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Developpeur Fullstack React Native Senior H/F</t>
+          <t>Tech Lead Java - Angular H/F</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/17/bc6a3fe664fa376e2dce9bd56cf87fb0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/14/6ea4a8aadb72d35272d90eb698589b9a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/19/d1979967f72255d6d0d448c6119a83d2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/16/7fa934aed9dd11309508bb5e4d7957cf/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Developpeur Fullstack React Native Senior H/F</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/32/54bdcdb876e53383d1d641fab6fe8b20/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/17/bc6a3fe664fa376e2dce9bd56cf87fb0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/33/cdec7311ff521c6dc3f9353d12ca19bb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/19/d1979967f72255d6d0d448c6119a83d2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/4/08a8487cbae35d0a569be92d54fb89e2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy92aXZlcmlzLTEwNTU2NC5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/32/54bdcdb876e53383d1d641fab6fe8b20/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/5/a171b6b20a7485a540572faabb8bcdd5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/ab7843b1-e019-4a6b-b8bd-f05bea92dad3/33/cdec7311ff521c6dc3f9353d12ca19bb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/7/1ec2e266aaf77c79db113ba07a88a5e7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/4/08a8487cbae35d0a569be92d54fb89e2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy92aXZlcmlzLTEwNTU2NC5odG1sP3V0bV9zb3VyY2U9bWFpbHNYam9iJnV0bV9tZWRpdW09ZW1haWwmdXRtX2NhbXBhaWduPWNhbmRpZGF0dXJlJnV0bV9jb250ZW50PXRvdXRzYXZvaXJzdXJsZW50cmVwcmlzZSN0b3V0c2F2b2lyc3VybGVudHJlcHJpc2U</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Développeur Java - Aws H/F</t>
+          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/8/26e29ff33ae43d01e92ced9d7ac757ee/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/5/a171b6b20a7485a540572faabb8bcdd5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/10/a4d3f1a412e18da9233146f785d53553/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/7/1ec2e266aaf77c79db113ba07a88a5e7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr"/>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
+          <t>Développeur Java - Aws H/F</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/11/8824ae09351cbfa17084f5f515c9480e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/8/26e29ff33ae43d01e92ced9d7ac757ee/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/13/413001903fc209a372bae8403044329a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/10/a4d3f1a412e18da9233146f785d53553/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr"/>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Java - Angular H/F</t>
+          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/14/9da2c368ecba55ed2ac74ddece328c59/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/11/8824ae09351cbfa17084f5f515c9480e/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/16/67c37e6257acf696264e1f3a0ddb4b01/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/13/413001903fc209a372bae8403044329a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Developpeur Fullstack React Native Senior H/F</t>
+          <t>Tech Lead Java - Angular H/F</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/17/6141be7324642e4ebb4e8462af77bbe8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/14/9da2c368ecba55ed2ac74ddece328c59/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/19/dc8fb7286da9dc4cfa37020c7eb8327b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/16/67c37e6257acf696264e1f3a0ddb4b01/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Developpeur Fullstack React Native Senior H/F</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/32/b54111f907958ddbf8039662ffff34e4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/17/6141be7324642e4ebb4e8462af77bbe8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/33/c38dac9ae5dcbe2cffb0cfa9f9027179/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/19/dc8fb7286da9dc4cfa37020c7eb8327b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyODAxNjYxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI4MDE2NjEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr"/>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/4/adf5b85caffef137ad00aa9ec2b02778/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9wcm90ZWN0aWMtMTg0NjQ3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX2NvbnRlbnQ9dG91dHNhdm9pcnN1cmxlbnRyZXByaXNlI3RvdXRzYXZvaXJzdXJsZW50cmVwcmlzZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/32/b54111f907958ddbf8039662ffff34e4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Java - Angular H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/5/6064e97cf259b66bdee734cefe85d40a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/6723c343-10f0-455f-be8c-d94960b75f1a/33/c38dac9ae5dcbe2cffb0cfa9f9027179/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr"/>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/7/9ffbc4cb5bdd31a63bc7161b87e9bf9b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/4/adf5b85caffef137ad00aa9ec2b02778/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9wcm90ZWN0aWMtMTg0NjQ3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX2NvbnRlbnQ9dG91dHNhdm9pcnN1cmxlbnRyZXByaXNlI3RvdXRzYXZvaXJzdXJsZW50cmVwcmlzZQ</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Java Angular H/F</t>
+          <t>Tech Lead Java - Angular H/F</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/8/f7163f6022b493e02af9ae7c2f692689/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQyMTEyLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDIxMTImdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/5/6064e97cf259b66bdee734cefe85d40a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/10/38556e40eab802b8ae8a0193833a36c6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQyMTEyLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDIxMTImdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/7/9ffbc4cb5bdd31a63bc7161b87e9bf9b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Développeur Java Confirmé H/F</t>
+          <t>Tech Lead Java Angular H/F</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/11/132a630c0daef49bda4317466ca18cd0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/8/f7163f6022b493e02af9ae7c2f692689/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQyMTEyLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDIxMTImdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/13/107bc3a18ddfc40b1c1ecb57478c81b6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/10/38556e40eab802b8ae8a0193833a36c6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQyMTEyLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDIxMTImdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr"/>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
+          <t>Développeur Java Confirmé H/F</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/14/3e6e4c5dd67c4678bf6aa6b0ed95e202/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/11/132a630c0daef49bda4317466ca18cd0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr"/>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/16/7d1bddb824c9331cd9ec1d1617a88621/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/13/107bc3a18ddfc40b1c1ecb57478c81b6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr"/>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
+          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/17/4af8d298558ff4321ee061afd29821e5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/14/3e6e4c5dd67c4678bf6aa6b0ed95e202/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr"/>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/19/0cd2fd0ef682e9c45ec1589665af803a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/16/7d1bddb824c9331cd9ec1d1617a88621/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/32/0bbe2abe0479648d0672ecdbfae2e5f5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/17/4af8d298558ff4321ee061afd29821e5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/33/203dadf59d03875b4ffaab5ae6519174/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/19/0cd2fd0ef682e9c45ec1589665af803a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/4/002489f30b0fbab5141ef8e381c00189/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy93aW5zaWRlLXRlY2hub2xvZ3ktMTUxMDg2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX2NvbnRlbnQ9dG91dHNhdm9pcnN1cmxlbnRyZXByaXNlI3RvdXRzYXZvaXJzdXJsZW50cmVwcmlzZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/32/0bbe2abe0479648d0672ecdbfae2e5f5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Développeur Java Confirmé H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/5/8f2007f96e106dc3993b3eb89fa274d8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/f8aa3afc-327c-4bd7-be0e-f13e8f5b8e0f/33/203dadf59d03875b4ffaab5ae6519174/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr"/>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/7/598b39e6c482de99499a7655d0fb6fc1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/4/002489f30b0fbab5141ef8e381c00189/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy93aW5zaWRlLXRlY2hub2xvZ3ktMTUxMDg2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX2NvbnRlbnQ9dG91dHNhdm9pcnN1cmxlbnRyZXByaXNlI3RvdXRzYXZvaXJzdXJsZW50cmVwcmlzZQ</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
+          <t>Développeur Java Confirmé H/F</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/8/fe9c3c50d58347269bef1fc122506e4d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/5/8f2007f96e106dc3993b3eb89fa274d8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr"/>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/10/dc0d2e91303cd835f5c5e3dc79b89116/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/7/598b39e6c482de99499a7655d0fb6fc1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Développeur Java - Aws H/F</t>
+          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/11/019a964f1e50a1e338fa970a1b95e23c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/8/fe9c3c50d58347269bef1fc122506e4d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr"/>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/13/80c73eb14be6cada40b1ebc6e6fda142/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/10/dc0d2e91303cd835f5c5e3dc79b89116/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
+          <t>Développeur Java - Aws H/F</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/14/1508b6660144bda9958223448ccb75f0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/11/019a964f1e50a1e338fa970a1b95e23c/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr"/>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/16/eb5cbf53a7fe99ce81077019f1b3cc97/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/13/80c73eb14be6cada40b1ebc6e6fda142/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Java - Angular H/F</t>
+          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/17/642a186c3f845b338649b576c31e48f6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/14/1508b6660144bda9958223448ccb75f0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/19/de427b8fe1968ec276da7a68c8dc170b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/16/eb5cbf53a7fe99ce81077019f1b3cc97/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Tech Lead Java - Angular H/F</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/32/be18428fffd11e6ad866c1c7fd69d680/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/17/642a186c3f845b338649b576c31e48f6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/33/fcb2db2b57af0c0bbcd1bf05c07d8b11/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/19/de427b8fe1968ec276da7a68c8dc170b/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr"/>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Développeur Java Confirmé H/F</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/3/344b3b3a683ae6b5ccc2475b68b527f7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/32/be18428fffd11e6ad866c1c7fd69d680/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr"/>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/5/ce8bee002e554313fb0089fd1be2fba3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/a07ee90c-6478-4225-b7fb-9cabcd092412/33/fcb2db2b57af0c0bbcd1bf05c07d8b11/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr"/>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
+          <t>Développeur Java Confirmé H/F</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/6/f8cc415326971c5b0b4f7e904e0e3075/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/3/344b3b3a683ae6b5ccc2475b68b527f7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/8/a3f3dd5c7910090c82b0f3d9077a5152/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/5/ce8bee002e554313fb0089fd1be2fba3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgxMDQ3NDAwLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODEwNDc0MDAmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr"/>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Développeur Java - Aws H/F</t>
+          <t>Dévloppeur Java - Python Openshift Senior H/F</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/9/de38ece280326a85e883dc548a7283c3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/6/f8cc415326971c5b0b4f7e904e0e3075/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/11/5f4bdde2d4850c8c7b1d4c8752ec35af/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/8/a3f3dd5c7910090c82b0f3d9077a5152/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyOTU2OTkxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI5NTY5OTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr"/>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
+          <t>Développeur Java - Aws H/F</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/12/c3e138b8ce8ed793432d96e1f080ecce/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/9/de38ece280326a85e883dc548a7283c3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr"/>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/14/24eea91f7c62ace3d7a09c67339d9a5d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/11/5f4bdde2d4850c8c7b1d4c8752ec35af/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzY2NzQwMzE0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NjY3NDAzMTQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead Java - Angular H/F</t>
+          <t>Consultant Java Backend Confirmé - Île-De-France H/F</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/15/5e6cdac5299abf575275ec0b181de576/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/12/c3e138b8ce8ed793432d96e1f080ecce/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr"/>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/17/2c70aed677294768615e5c4170b546f4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/14/24eea91f7c62ace3d7a09c67339d9a5d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMjE0ODk3Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIyMTQ4OTcmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Tech Lead Java - Angular H/F</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/30/221accd6cfef45c73589b1919d591de5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/15/5e6cdac5299abf575275ec0b181de576/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr"/>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/31/f2178ebd7b85c62436bd9a0c13fd7f17/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/17/2c70aed677294768615e5c4170b546f4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMTc3NDAxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIxNzc0MDEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr"/>
@@ -6102,17 +6102,17 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Développeur back-end Sylius senior (H/F)</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://apply.indeed.com/indeedapply/confirmemail/viewjob?iaUid=1k2626nfojbp5801&amp;apiToken=aa102235a5ccb18bd3668c0e14aa3ea7e2503cfac2a7a9bf3d6549899e125af4&amp;next=https%3A%2F%2Ffr.indeed.com%2Fviewjob%3Fjk%3D3434f85229218170</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/30/221accd6cfef45c73589b1919d591de5/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr"/>
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Apprenez à reconnaître les emails frauduleux</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://apply.indeed.com/indeedapply/confirmemail/fraudlink?iaUid=1k2626nfojbp5801&amp;apiToken=aa102235a5ccb18bd3668c0e14aa3ea7e2503cfac2a7a9bf3d6549899e125af4</t>
+          <t>https://emails.hellowork.com/clic/8210960f-0891-4ca8-8d54-78960f97f86b/31/f2178ebd7b85c62436bd9a0c13fd7f17/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr"/>
@@ -6148,17 +6148,17 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Développeur back-end Sylius senior (H/F)</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/4/f16d21975e85d86ba162db358175b758/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9nZnAtdGVjaC0xMTY5MTUuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD10b3V0c2F2b2lyc3VybGVudHJlcHJpc2UjdG91dHNhdm9pcnN1cmxlbnRyZXByaXNl</t>
+          <t>https://apply.indeed.com/indeedapply/confirmemail/viewjob?iaUid=1k2626nfojbp5801&amp;apiToken=aa102235a5ccb18bd3668c0e14aa3ea7e2503cfac2a7a9bf3d6549899e125af4&amp;next=https%3A%2F%2Ffr.indeed.com%2Fviewjob%3Fjk%3D3434f85229218170</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr"/>
@@ -6171,17 +6171,17 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead PHP - Drupal - Angular H/F</t>
+          <t>Apprenez à reconnaître les emails frauduleux</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
+          <t>Alerte email — Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/5/a5a9661e1bd1854e1dd73e5eea7d7a47/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://apply.indeed.com/indeedapply/confirmemail/fraudlink?iaUid=1k2626nfojbp5801&amp;apiToken=aa102235a5ccb18bd3668c0e14aa3ea7e2503cfac2a7a9bf3d6549899e125af4</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr"/>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/7/e0d4f1af24f57215e636cdac5969c6e4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/4/f16d21975e85d86ba162db358175b758/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9nZnAtdGVjaC0xMTY5MTUuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD10b3V0c2F2b2lyc3VybGVudHJlcHJpc2UjdG91dHNhdm9pcnN1cmxlbnRyZXByaXNl</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr"/>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Chef de Projet Développeur Full Stack H/F</t>
+          <t>Tech Lead PHP - Drupal - Angular H/F</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/8/88559f853d5a3f135e6b9d3c9f8e81b0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/5/a5a9661e1bd1854e1dd73e5eea7d7a47/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr"/>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/10/b2b41f063155a36f155686f515285d77/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/7/e0d4f1af24f57215e636cdac5969c6e4/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr"/>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Développeur PHP React H/F</t>
+          <t>Chef de Projet Développeur Full Stack H/F</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/11/c82714207ffdc730a0db5614a68e97e1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/8/88559f853d5a3f135e6b9d3c9f8e81b0/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr"/>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/13/5de17b283817698a6128ddbf3018b2a2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/10/b2b41f063155a36f155686f515285d77/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr"/>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Développeur Full Stack Java Angular H/F</t>
+          <t>Développeur PHP React H/F</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/14/4cca7965a9525bdf27575e8b458d6bf8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/11/c82714207ffdc730a0db5614a68e97e1/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr"/>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/16/efaa04159da77dbbf578e97eefc1e8d6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/13/5de17b283817698a6128ddbf3018b2a2/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr"/>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Developpeur Fullstack Senior - Rédaction des Procédures H/F</t>
+          <t>Développeur Full Stack Java Angular H/F</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/17/0f90bf3536a8fc876f4c367d266b3ed7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/14/4cca7965a9525bdf27575e8b458d6bf8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr"/>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/19/9f0be774b28f2b06acac312c930e1e3a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/16/efaa04159da77dbbf578e97eefc1e8d6/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr"/>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Developpeur Fullstack Senior - Rédaction des Procédures H/F</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/32/77550ea12398059d7ebe85aab3d36934/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/17/0f90bf3536a8fc876f4c367d266b3ed7/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr"/>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/33/467be8c8831fc3edcb6ecd8f2f42cb89/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/19/9f0be774b28f2b06acac312c930e1e3a/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr"/>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Tout savoir sur l'entreprise</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/4/1914ecc70fdd37f4888d53b7dd2dc09d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9nZnAtdGVjaC0xMTY5MTUuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD10b3V0c2F2b2lyc3VybGVudHJlcHJpc2UjdG91dHNhdm9pcnN1cmxlbnRyZXByaXNl</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/32/77550ea12398059d7ebe85aab3d36934/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Tech Lead PHP - Drupal - Angular H/F</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/5/5f7972d49b8e657ae959a590d6ac5488/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/98074dc8-351e-45d2-8978-7acf1aae712f/33/467be8c8831fc3edcb6ecd8f2f42cb89/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr"/>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Voir l’offre</t>
+          <t>Tout savoir sur l'entreprise</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/7/18bd52bd3ed1f61d907b43372cec2245/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/4/1914ecc70fdd37f4888d53b7dd2dc09d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbnRyZXByaXNlcy9nZnAtdGVjaC0xMTY5MTUuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD10b3V0c2F2b2lyc3VybGVudHJlcHJpc2UjdG91dHNhdm9pcnN1cmxlbnRyZXByaXNl</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Chef de Projet Développeur Full Stack H/F</t>
+          <t>Tech Lead PHP - Drupal - Angular H/F</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/8/f48087ef65fe6042f5b878a58c1c8198/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/5/5f7972d49b8e657ae959a590d6ac5488/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr"/>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/10/62cb650bbd867e3c69d2537d221c5733/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/7/18bd52bd3ed1f61d907b43372cec2245/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzcyODEyNzUxLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09NzI4MTI3NTEmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Développeur PHP React H/F</t>
+          <t>Chef de Projet Développeur Full Stack H/F</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/11/8a88498347ccaf4d120d9ed65e619f37/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/8/f48087ef65fe6042f5b878a58c1c8198/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/13/5b7bc89cba0f762254e6909c091693cb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/10/62cb650bbd867e3c69d2537d221c5733/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNzkwNTI0Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI3OTA1MjQmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Développeur Full Stack Java Angular H/F</t>
+          <t>Développeur PHP React H/F</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/14/5cc6905b1f32499bcd0436d8fb6d779d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/11/8a88498347ccaf4d120d9ed65e619f37/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/16/56230451618af3401da55f84164d9f57/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/13/5b7bc89cba0f762254e6909c091693cb/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyMDI0NDA2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODIwMjQ0MDYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Developpeur Fullstack Senior - Rédaction des Procédures H/F</t>
+          <t>Développeur Full Stack Java Angular H/F</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/17/76c05f86c1ddc2eaaf8537f503795d6d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/14/5cc6905b1f32499bcd0436d8fb6d779d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/19/3932b3627829df90bec5fad9a3ec3295/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/16/56230451618af3401da55f84164d9f57/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgyNTQ5OTE1Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODI1NDk5MTUmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr"/>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Espace candidat</t>
+          <t>Developpeur Fullstack Senior - Rédaction des Procédures H/F</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/32/b2c83f60f94f00d8d1f88915b4dd10b3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/17/76c05f86c1ddc2eaaf8537f503795d6d/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9aW50aXR1bGVvZmZyZQ</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr"/>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Aide et contact</t>
+          <t>Voir l’offre</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/33/764bba85da2dc55726873416e2d015a8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/19/3932b3627829df90bec5fad9a3ec3295/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9lbXBsb2lzLzgwMDc0OTI2Lmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmUmdXRtX3Rlcm09ODAwNzQ5MjYmdXRtX2NvbnRlbnQ9dm9pcmxvZmZyZQ</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr"/>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Voir l'emploi</t>
+          <t>Espace candidat</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
+          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32UW6-qSBCF_4vJ-DScTXMTdmImCshFRREB5YVA09yaiyBXT85_H855mMdJV9LJtypVqYe1fq761fcq7brX-_vrK25_ZFWEUPQD1uXXK0hQEH3BAv8Tt3W5zeswowJ_-cqggykRt8Th5qMyyIp13nZ4yxKwTAGxPExxIGNQQCd9SZKAYCALKJ7mwIYlOcBt1mW9bddBtCU441mEMTZI6WnNg5DS5QNYAQr9m2iY8oPK85P1IdIK2e8ebLzwGo5RtCl9UDfkx0wqQWZ7zMbvKqbOQK4dWVMHzeSjMRirEiushALNYyY92Zn3hulCP7w4kUXxBFHoykGkjNIJddDzB9bPNxflWYDZGjds8QwnfjxlF9soC0K7M3pxVHdnBVcV3h0zgfi88vR-frAm-W6mPsR2E-tClO9fvG69zafa88nV3R-9eSo3gSg6pW_ifr6dnCFijfHxcsTn7Hjz0Rbcmkttwuka32WFLmtyOYdJIQt74rLcItG5nIVmyBnqpLTXCWZZ0NObnreOGGgPC-iicz5sIjrtUE4Q12aZ7GlsDnwapr73GXhUZ9HHriSZhQIhwyLHJu8Oqm8haHI7LrgphwFOnHWyuS4t3vJRmWfKu96MDeg3sWwKpSWQumG9Ic-C8Z5-HCLGjFTqm7Tr-3bW3Fi8UzeUZifX9GB9oVm2aW-13dQvAnG0U-5C2yHpJkGDqD56v4rcO3V3YEkOkwJfOFMuZ7GZjuIVN6REuaB96x4yPSZlpfYIJiqOXISGZifKmjfOodON2acwmL2zfw-Vj_Mu7KwquTxJTBC5feIQTWWI2lNaccn2hSKO831gbzXGOXN-AlWRVDVoP291ALUCpMo5Tv4Nol3SOrYRRIVGIkRYk12KxYUaG85BDbKz5ywaevyoNGC-LOXwBIZpWeIpb0pwu5ux4w7PvStNQjbf3DOc-3Nf-sghwrAv-M8hoGEdMIgRLvYA8DDl5zBWVAGs23JLrScMw61VSxTnnymknNTIn3fHPXkJPzgSo-t1nb-DrUCTYA2DEm_t-tgp3imgH6czNZkZAQT1lfxFS0ut_l6Vq--fqwDCuq86LVr8zQgCT_OkwC1ikCR6Hf7BgKTYxZMCx5GLAIsM4nva1n2SLmLX9ug_Or_QgoYMjYv7F_o7DxbwP4mwNHX4944_UcAKQ1L3LU-C1a9f_wJRZLNXdAQAAA/Qbs7SB3I-BKKsla5k3Bd5Ex9deh1RR6PPB5u6zqP25s</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/32/b2c83f60f94f00d8d1f88915b4dd10b3/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9jYW5kaWRhdC9tb24tcHJvZmlsLmh0bWw_dXRtX3NvdXJjZT1tYWlsc1hqb2ImdXRtX21lZGl1bT1lbWFpbCZ1dG1fY2FtcGFpZ249Y2FuZGlkYXR1cmU</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr"/>
@@ -6769,17 +6769,17 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Ne correspond pas</t>
+          <t>Aide et contact</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
+          <t>Alerte email — Hellowork Candidature &lt;contact@emails.hellowork.com&gt;</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QQW-CMBiG_0sPO41ZrDJqsiwiziljOkc0nkiBAgVppbTb0Oy_r_Oww77LlzzPm7zJewEaTECp1KmbDAYNUWl5x3hGaXaXimbA-AdTRDHBuwEXymJcUUk7RbNHVT_Y9dCx2Rh_FEJLF9o3jOfiYfp7O7Ii3r5aJvwrs8ho3u1naBeUi3dvL7FaVk9zt4tf0FuCAz-Clneqhc9R68teduecZXjN19amDnBc3Z87KrwhOR_bz69wOuZotiDQ-bS36KAP0SgIdUukt13mEQ1G7txuw3lbiUbN7rPet1dpjDb9IVyk0IlmZN-NNSw0fAl302f67Pfnw2uJNH9_Y5uiLRqyQhuO4_LVXcSeB25BAyYXQNJUaK6WmRlrhLGLXIgdI0lRrERyxTYcjpFjY8eBRqRHltZRKYUuSiOV1PSP9idqUEIy67q34bkUpgZUImFDEpt3FVYuradtTBvCjiak6t-Wf5OD7-8fuxykR8MBAAA/zE8g_A7IoL4M5_QRSqz0OeGa2YAK0xnZxHA2eiHun7Y</t>
+          <t>https://emails.hellowork.com/clic/e76e832f-93c1-464e-a62b-b8d2cbe861ac/33/764bba85da2dc55726873416e2d015a8/MjA0Ym91YWtpLmFydGh1ckBnbWFpbC5jb23wn6qiaHR0cHM6Ly93d3cuaGVsbG93b3JrLmNvbS9mci1mci9wYWdlL2NvbnRhY3QuaHRtbD91dG1fc291cmNlPW1haWxzWGpvYiZ1dG1fbWVkaXVtPWVtYWlsJnV0bV9jYW1wYWlnbj1jYW5kaWRhdHVyZSZ1dG1fY29udGVudD1jb250YWN0</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr"/>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Modifier le profil</t>
+          <t>Voir l'emploi</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_0sGp0arbcUI0k3oKt0l5sOkSYzEN4Ui_vdmKJ0O7h7ubkcRtUgBrFtbFGvwUluR64ULwXPm3V0G77qXn3RFxySOAlNYBtwPo3BU24z5rh8yZTsZ0Ak51O6IMubjAg-eqq-ENJfmTOoUMquZearg46xSBCGKv_tZRbI2RwNgmcYnygwWXAP-nUokmISUpqpLfSPv2cfQnEt0HF_aiXOKxQAAAA/C3WdBm9n9XCoPo9i7PP6i_wejB7gvA9MpaBvoAoG_gs</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32UW6-qSBCF_4vJ-DScTXMTdmImCshFRREB5YVA09yaiyBXT85_H855mMdJV9LJtypVqYe1fq761fcq7brX-_vrK25_ZFWEUPQD1uXXK0hQEH3BAv8Tt3W5zeswowJ_-cqggykRt8Th5qMyyIp13nZ4yxKwTAGxPExxIGNQQCd9SZKAYCALKJ7mwIYlOcBt1mW9bddBtCU441mEMTZI6WnNg5DS5QNYAQr9m2iY8oPK85P1IdIK2e8ebLzwGo5RtCl9UDfkx0wqQWZ7zMbvKqbOQK4dWVMHzeSjMRirEiushALNYyY92Zn3hulCP7w4kUXxBFHoykGkjNIJddDzB9bPNxflWYDZGjds8QwnfjxlF9soC0K7M3pxVHdnBVcV3h0zgfi88vR-frAm-W6mPsR2E-tClO9fvG69zafa88nV3R-9eSo3gSg6pW_ifr6dnCFijfHxcsTn7Hjz0Rbcmkttwuka32WFLmtyOYdJIQt74rLcItG5nIVmyBnqpLTXCWZZ0NObnreOGGgPC-iicz5sIjrtUE4Q12aZ7GlsDnwapr73GXhUZ9HHriSZhQIhwyLHJu8Oqm8haHI7LrgphwFOnHWyuS4t3vJRmWfKu96MDeg3sWwKpSWQumG9Ic-C8Z5-HCLGjFTqm7Tr-3bW3Fi8UzeUZifX9GB9oVm2aW-13dQvAnG0U-5C2yHpJkGDqD56v4rcO3V3YEkOkwJfOFMuZ7GZjuIVN6REuaB96x4yPSZlpfYIJiqOXISGZifKmjfOodON2acwmL2zfw-Vj_Mu7KwquTxJTBC5feIQTWWI2lNaccn2hSKO831gbzXGOXN-AlWRVDVoP291ALUCpMo5Tv4Nol3SOrYRRIVGIkRYk12KxYUaG85BDbKz5ywaevyoNGC-LOXwBIZpWeIpb0pwu5ux4w7PvStNQjbf3DOc-3Nf-sghwrAv-M8hoGEdMIgRLvYA8DDl5zBWVAGs23JLrScMw61VSxTnnymknNTIn3fHPXkJPzgSo-t1nb-DrUCTYA2DEm_t-tgp3imgH6czNZkZAQT1lfxFS0ut_l6Vq--fqwDCuq86LVr8zQgCT_OkwC1ikCR6Hf7BgKTYxZMCx5GLAIsM4nva1n2SLmLX9ug_Or_QgoYMjYv7F_o7DxbwP4mwNHX4944_UcAKQ1L3LU-C1a9f_wJRZLNXdAQAAA/Qbs7SB3I-BKKsla5k3Bd5Ex9deh1RR6PPB5u6zqP25s</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Suspendre ces emails</t>
+          <t>Ne correspond pas</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QQW-CMABG_0sPO00Bi0pNzCLCUBmKSiSeSAWEgrQCrQrG_z62ww77bt97t_cEAkxAyvm1nkhSgXmY9gmN4jjqh6yQCL0RjjlhtJauWNTxB8-nSj4YKWSIbgkTlSYrb4Se2XT2swNeYd3Plif6iHpYNWt_Dg92au11v0J8mX2aWh18we0J2YYn9_RrzgwKS6Nqqro9kwht6Kbn5jYKsnFbx0wf4PZS3h_ObEjh3MLy6K7s4FEcPdV2RIkrfbc8e7GtaqZSOmaZsYLPx1FjKKswgG5zdKxQHnlz7NdDISdC_nIOs0W8MJr2uE6hoPstcZMyKfAKuhQF6VqzAl0H76AAkyfAYcgE5cuoa6QipEFNRqNOhhcS5l5aMZGkneKViP9oc4079BurYzzvzv9g4PX6BsdDPN54AQAA/o2k-1uIxB0aeAGQGE8Ld2aQ-EX1Pj0eZ0IcOi8ALxG8</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QQW-CMBiG_0sPO41ZrDJqsiwiziljOkc0nkiBAgVppbTb0Oy_r_Oww77LlzzPm7zJewEaTECp1KmbDAYNUWl5x3hGaXaXimbA-AdTRDHBuwEXymJcUUk7RbNHVT_Y9dCx2Rh_FEJLF9o3jOfiYfp7O7Ii3r5aJvwrs8ho3u1naBeUi3dvL7FaVk9zt4tf0FuCAz-Clneqhc9R68teduecZXjN19amDnBc3Z87KrwhOR_bz69wOuZotiDQ-bS36KAP0SgIdUukt13mEQ1G7txuw3lbiUbN7rPet1dpjDb9IVyk0IlmZN-NNSw0fAl302f67Pfnw2uJNH9_Y5uiLRqyQhuO4_LVXcSeB25BAyYXQNJUaK6WmRlrhLGLXIgdI0lRrERyxTYcjpFjY8eBRqRHltZRKYUuSiOV1PSP9idqUEIy67q34bkUpgZUImFDEpt3FVYuradtTBvCjiak6t-Wf5OD7-8fuxykR8MBAAA/zE8g_A7IoL4M5_QRSqz0OeGa2YAK0xnZxHA2eiHun7Y</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr"/>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Centre d'aide</t>
+          <t>Modifier le profil</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MywqDMBBF_2XWxZg-JBGK6-77AyWJJkRNGGcKRfz3zqJ0ec_h3B0YeohEdeuV2rjWgtSk1YfgG1cWFZ0acYjzfUQ4wQL9Di_nCq_08FJerTUX09pOpJuTy8-IhacoipDDn35qEPT7F0pZps7nTqebfU-F0bQajuMLiQihS5AAAAA/KsbrQFO2hSjh-J5RLUO-RPs9Q7ZfVRi5kwFqaWWKNpY</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_0sGp0arbcUI0k3oKt0l5sOkSYzEN4Ui_vdmKJ0O7h7ubkcRtUgBrFtbFGvwUluR64ULwXPm3V0G77qXn3RFxySOAlNYBtwPo3BU24z5rh8yZTsZ0Ak51O6IMubjAg-eqq-ENJfmTOoUMquZearg46xSBCGKv_tZRbI2RwNgmcYnygwWXAP-nUokmISUpqpLfSPv2cfQnEt0HF_aiXOKxQAAAA/C3WdBm9n9XCoPo9i7PP6i_wejB7gvA9MpaBvoAoG_gs</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr"/>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Conditions d'utilisation</t>
+          <t>Suspendre ces emails</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MywrDIBBF_2W6LTH2EVQoXXffHwhqVNQYJmOhhPx7zabLew7nblBBgSdaVsXYhF2YjbWm0yWzZN2Ynj49JjxRWeEMGdQGo9alzvQyLbxJKa6il0OTOgUd3x5Ldb4pwmr_9LvYA1nMxw3FNni8DDzc5ceViqLnsO8_v0dI1I0AAAA/5nYi0WJYPxnLxyetCxavNFF1sCTK0XKNVPy0wsWz_D8</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QQW-CMABG_0sPO00Bi0pNzCLCUBmKSiSeSAWEgrQCrQrG_z62ww77bt97t_cEAkxAyvm1nkhSgXmY9gmN4jjqh6yQCL0RjjlhtJauWNTxB8-nSj4YKWSIbgkTlSYrb4Se2XT2swNeYd3Plif6iHpYNWt_Dg92au11v0J8mX2aWh18we0J2YYn9_RrzgwKS6Nqqro9kwht6Kbn5jYKsnFbx0wf4PZS3h_ObEjh3MLy6K7s4FEcPdV2RIkrfbc8e7GtaqZSOmaZsYLPx1FjKKswgG5zdKxQHnlz7NdDISdC_nIOs0W8MJr2uE6hoPstcZMyKfAKuhQF6VqzAl0H76AAkyfAYcgE5cuoa6QipEFNRqNOhhcS5l5aMZGkneKViP9oc4079BurYzzvzv9g4PX6BsdDPN54AQAA/o2k-1uIxB0aeAGQGE8Ld2aQ-EX1Pj0eZ0IcOi8ALxG8</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr"/>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Voir l'emploi</t>
+          <t>Centre d'aide</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32TSaujaBSG_0ugs2rrOg8XQhONGo3GKYnDRhw-jbN-xilF_fdK9aKXDQcOPO8Lh7N4fu6m3ffu-Xr14_fXVwZ_FG0KQPoj6ZqvPspBlH4ldfVPBrvmUHZxgUfhZ43dBBMAkQwikh2CJirqfdMd4D5KDwh99es4q64on5neJcRnrfFo-imcbmizOu7zuDY8trUcsQiB7wisVR8twxNKC2cKLPNLTSQGA14o1bcvKjeatDxTKpb7Qg7SKoqfUAK3TYzvPWCGs3_GWt8ac_91j5Zo1Xk-vyUIrpw61yjtmshis7vbpW-UPoaQ_BhK8M5qkClkgfFtK4zjudcxSlLSyWxTiNr3ayAjW7aROpA2cwiGgjwL5sBYeLyY0UT0LLK53RhClzquOZBz8fwouDzBjHRaEEud7vT8bF-ROTGqcfSFCe0mDGXrOdVEXxRSVhEVuczHSVGC9ta0ng7Mk6ZXDw7UAfMwGI2wqDZOLEYZ51WWndDHNMWl58sAAiU-1jdWFJ2kbuRZWQ07vtitBGGkJqWGYM5czs_Z8Rw4ULdWXd7m1U5Z-o2iitqT4bmeNKlb6BPDndwtGIW2Epyif9znluXCErWUitbSy-IJuVNF5dJWFespQ3hxG5CRmNKPKeQKQukkPbYeVr_UnMPr69raQ35utea6sezzKvqX7k4z59OtxrVHjKuKNIDN5p9SxLotMbUkxXms__l4OK701uDSe0noFk6Te9fzNh4CxDgFgyBBJhcUzkofNnb3hPtAtKbHeEWjHZFcnZfFtOW5lwk6Qq8OD-2ASUfq3SSuTta4R84C570HC-Px5uyIiTKyoVYjHT1SdrIQs5LZY8GrUXA-3-jV6oltnIytuMLq0m1ertm9zRpcQUlu5oFhOiE4UHVGx6H18laUn5hl5vvXBsr5ArK3Q5ikjKdEkvZ72Bzw_Vol8cHpTjkd6jiQiBbr3AsToGb8rlIhNc19OUYHDsfQfRI11UEgRNN5S7W1IKJdeJV-RFLp-Bdx-szu712z-_65i5Kkm9qXkn6MJTmOJViUoz9hlOdqF_-LMRSnWI5kKeJPkNRFUt2esJvy5yd8wQn8R7cefNBcgOXj84f-MfwD_tfxT-1V_blS4dQ8oDFTvbKKRbHdr1-_AXRcfD1IBAAA/mz-CnGBhjVRKqg6eLnvUr3aBUQAau4xJ_PQaATs_m9U</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MywqDMBBF_2XWxZg-JBGK6-77AyWJJkRNGGcKRfz3zqJ0ec_h3B0YeohEdeuV2rjWgtSk1YfgG1cWFZ0acYjzfUQ4wQL9Di_nCq_08FJerTUX09pOpJuTy8-IhacoipDDn35qEPT7F0pZps7nTqebfU-F0bQajuMLiQihS5AAAAA/KsbrQFO2hSjh-J5RLUO-RPs9Q7ZfVRi5kwFqaWWKNpY</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Ne correspond pas</t>
+          <t>Conditions d'utilisation</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QQW-qQBSF_8ss3upRERQHk-ZFQCK2aLFI7duQYRhgQGdgGERt-t-LXXTRu7nJ953kJOcDdGAOCinrdj4anZDExQNlKSHpA-anEWVnKpGknLUjxqVCmSSCtJKk_2T1OK606blRk1klswqq4z-UZfxxcT8UFqF4tlqlvwWcXVayW048P89KzdjWJOuDQE_sa6Pk-1sQBIX3VrrofWFYfpTtZ2H0HtWevXfI-rgZW43jz5rScA_5Vf2_PjtLbstVmURZgl0isOfHL7euXC1dZHL7osCt8rSB6Xbr9yH2KxZ7N_cJ9a-v0KO7eGpGlabvnq2d44l4cZxBJ7FtmRwMmKXQF-t6g5jb6Nbb8tBj8BecwPwDIIx5x6SXDmNNTBPqUDWNQaI8X_PkG49VbQrNCZzqd4GPFFdhIXiXF4OUoiM_9FqTASUoVb73Hngm-FADSp5QDcXDa3knMBFKJhR3F5MToschJqt7z6_RwefnF13FIyvFAQAA/VuGiAjrKzcJvsjwD4q71GMlg30EYn6F6YatFU0Hon60</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MywrDIBBF_2W6LTH2EVQoXXffHwhqVNQYJmOhhPx7zabLew7nblBBgSdaVsXYhF2YjbWm0yWzZN2Ynj49JjxRWeEMGdQGo9alzvQyLbxJKa6il0OTOgUd3x5Ldb4pwmr_9LvYA1nMxw3FNni8DDzc5ceViqLnsO8_v0dI1I0AAAA/5nYi0WJYPxnLxyetCxavNFF1sCTK0XKNVPy0wsWz_D8</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr"/>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Modifier le profil</t>
+          <t>Voir l'emploi</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_8s7ODVW7ZcK0k3oKt0lxqRJkxj7mhSK-N-boXQ6uHu4uxUC1CC9n5d6v5_RCWV4qqaR8zFlzl4FOts83aAK2kdZXEDGkQgkbddzS5VJmGvaLpGmEQg7sFCvQBlzYfK3MZYfq6o8lFl1jiEzium7RBceMkYeA_-7n5lHa7EUPRFxfqBMEz4qT363Iul1RHJdnN6vbLhoL3SZ5bBtX8ukexjHAAAA/vo0vlVxA07BrqSl-jedc9cSeUcSFaNex9L27UPTmiiI</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32TSaujaBSG_0ugs2rrOg8XQhONGo3GKYnDRhw-jbN-xilF_fdK9aKXDQcOPO8Lh7N4fu6m3ffu-Xr14_fXVwZ_FG0KQPoj6ZqvPspBlH4ldfVPBrvmUHZxgUfhZ43dBBMAkQwikh2CJirqfdMd4D5KDwh99es4q64on5neJcRnrfFo-imcbmizOu7zuDY8trUcsQiB7wisVR8twxNKC2cKLPNLTSQGA14o1bcvKjeatDxTKpb7Qg7SKoqfUAK3TYzvPWCGs3_GWt8ac_91j5Zo1Xk-vyUIrpw61yjtmshis7vbpW-UPoaQ_BhK8M5qkClkgfFtK4zjudcxSlLSyWxTiNr3ayAjW7aROpA2cwiGgjwL5sBYeLyY0UT0LLK53RhClzquOZBz8fwouDzBjHRaEEud7vT8bF-ROTGqcfSFCe0mDGXrOdVEXxRSVhEVuczHSVGC9ta0ng7Mk6ZXDw7UAfMwGI2wqDZOLEYZ51WWndDHNMWl58sAAiU-1jdWFJ2kbuRZWQ07vtitBGGkJqWGYM5czs_Z8Rw4ULdWXd7m1U5Z-o2iitqT4bmeNKlb6BPDndwtGIW2Epyif9znluXCErWUitbSy-IJuVNF5dJWFespQ3hxG5CRmNKPKeQKQukkPbYeVr_UnMPr69raQ35utea6sezzKvqX7k4z59OtxrVHjKuKNIDN5p9SxLotMbUkxXms__l4OK701uDSe0noFk6Te9fzNh4CxDgFgyBBJhcUzkofNnb3hPtAtKbHeEWjHZFcnZfFtOW5lwk6Qq8OD-2ASUfq3SSuTta4R84C570HC-Px5uyIiTKyoVYjHT1SdrIQs5LZY8GrUXA-3-jV6oltnIytuMLq0m1ertm9zRpcQUlu5oFhOiE4UHVGx6H18laUn5hl5vvXBsr5ArK3Q5ikjKdEkvZ72Bzw_Vol8cHpTjkd6jiQiBbr3AsToGb8rlIhNc19OUYHDsfQfRI11UEgRNN5S7W1IKJdeJV-RFLp-Bdx-szu712z-_65i5Kkm9qXkn6MJTmOJViUoz9hlOdqF_-LMRSnWI5kKeJPkNRFUt2esJvy5yd8wQn8R7cefNBcgOXj84f-MfwD_tfxT-1V_blS4dQ8oDFTvbKKRbHdr1-_AXRcfD1IBAAA/mz-CnGBhjVRKqg6eLnvUr3aBUQAau4xJ_PQaATs_m9U</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr"/>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Suspendre ces emails</t>
+          <t>Ne correspond pas</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qu3KCQABF_4UiVRAVhcUZJyOvcVUkKKKmYZbljbI8FlEc_z0kRYrc7p7TnSfTMDMmprSoZxx3RRTHgyT3g8AfYHLlkvyWUEQTktdcgZo6-KDZfJSNp7dy6IkZDTMwHL0leUjmi58hO7arjVyzbWeR_L6kjTaBRhSmY8EsgrC1LN5THiUbHTrLsmJ4THV0Xgiy4YQH0XbOTgGVgxqsLtuRXKqGWKaCfooew6_VTdWIQpep54Qe1oMKQ8P97Jp0qelIIsqdBSa73gLfNI3WxkaWu7DT16jd7wFMdu5UcrIxv9vIOxVW7uIiAtVTFOqdBBD6wKhWxRblesnLR-3UYuaduTKzJ4MwJk1Ood83mkgS4MFQEnqJLwnO7LgiTRT3ilZN8EcfRdCj31g9o1l__gdjXq9v_da7UXgBAAA/HlTUctBFWPyrOQfEXoL-IZ_ThyTRmg5TPyQ9ZewT9g8</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QQW-qQBSF_8ss3upRERQHk-ZFQCK2aLFI7duQYRhgQGdgGERt-t-LXXTRu7nJ953kJOcDdGAOCinrdj4anZDExQNlKSHpA-anEWVnKpGknLUjxqVCmSSCtJKk_2T1OK606blRk1klswqq4z-UZfxxcT8UFqF4tlqlvwWcXVayW048P89KzdjWJOuDQE_sa6Pk-1sQBIX3VrrofWFYfpTtZ2H0HtWevXfI-rgZW43jz5rScA_5Vf2_PjtLbstVmURZgl0isOfHL7euXC1dZHL7osCt8rSB6Xbr9yH2KxZ7N_cJ9a-v0KO7eGpGlabvnq2d44l4cZxBJ7FtmRwMmKXQF-t6g5jb6Nbb8tBj8BecwPwDIIx5x6SXDmNNTBPqUDWNQaI8X_PkG49VbQrNCZzqd4GPFFdhIXiXF4OUoiM_9FqTASUoVb73Hngm-FADSp5QDcXDa3knMBFKJhR3F5MToschJqt7z6_RwefnF13FIyvFAQAA/VuGiAjrKzcJvsjwD4q71GMlg30EYn6F6YatFU0Hon60</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr"/>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Centre d'aide</t>
+          <t>Modifier le profil</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2Myw7CIBBF_2XWplCfQGJcd98f0AGkoS1IBxPT9N-dhXF5z8m5K1QwEIjyYoRYas6pUDPM1jnbYJpEQOHLLYxXX2AHE5gV7oipztRZLo9aq4OS-swSxwFjH0qqz8CKSnV_-smO0e-fKUWebdyf3i_5uETyUckWtu0Lj7KjFZAAAAA/kW1RUyO1EHwzw6aaOden_jmsGUKsiXTShjgETHDzYzw</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_8s7ODVW7ZcK0k3oKt0lxqRJkxj7mhSK-N-boXQ6uHu4uxUC1CC9n5d6v5_RCWV4qqaR8zFlzl4FOts83aAK2kdZXEDGkQgkbddzS5VJmGvaLpGmEQg7sFCvQBlzYfK3MZYfq6o8lFl1jiEzium7RBceMkYeA_-7n5lHa7EUPRFxfqBMEz4qT363Iul1RHJdnN6vbLhoL3SZ5bBtX8ukexjHAAAA/vo0vlVxA07BrqSl-jedc9cSeUcSFaNex9L27UPTmiiI</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr"/>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Conditions d'utilisation</t>
+          <t>Suspendre ces emails</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2Myw7CIBBF_2XcmkJ9Aolx7d4fqDCUBiiVDiam6b9LNy7vOTl3gQIKHNE0K8ZsbobRIJpGp8gC9l24u3CzeUdphj1EUAt0Wqcy0sPU8CSlOAouL1XqMGj_dDmV3lVFueCffifcEOa43ZCvo_WH8-fNX1dP1gvewrr-ALn9SoqNAAAA/ulGitdpRG6-tZ8pccyrPFSeZfwN7ufnIBapuqRNJiEA</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qu3KCQABF_4UiVRAVhcUZJyOvcVUkKKKmYZbljbI8FlEc_z0kRYrc7p7TnSfTMDMmprSoZxx3RRTHgyT3g8AfYHLlkvyWUEQTktdcgZo6-KDZfJSNp7dy6IkZDTMwHL0leUjmi58hO7arjVyzbWeR_L6kjTaBRhSmY8EsgrC1LN5THiUbHTrLsmJ4THV0Xgiy4YQH0XbOTgGVgxqsLtuRXKqGWKaCfooew6_VTdWIQpep54Qe1oMKQ8P97Jp0qelIIsqdBSa73gLfNI3WxkaWu7DT16jd7wFMdu5UcrIxv9vIOxVW7uIiAtVTFOqdBBD6wKhWxRblesnLR-3UYuaduTKzJ4MwJk1Ood83mkgS4MFQEnqJLwnO7LgiTRT3ilZN8EcfRdCj31g9o1l__gdjXq9v_da7UXgBAAA/HlTUctBFWPyrOQfEXoL-IZ_ThyTRmg5TPyQ9ZewT9g8</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Connexion</t>
+          <t>Centre d'aide</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>https://secure.indeed.com/account/login?continue=https%3A%2F%2Ffr.indeed.com%2F&amp;from=jobi2a_multijob-fr-FR_email&amp;tk=1k25j6726l2fh801&amp;co=FR&amp;hl=fr</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2Myw7CIBBF_2XWplCfQGJcd98f0AGkoS1IBxPT9N-dhXF5z8m5K1QwEIjyYoRYas6pUDPM1jnbYJpEQOHLLYxXX2AHE5gV7oipztRZLo9aq4OS-swSxwFjH0qqz8CKSnV_-smO0e-fKUWebdyf3i_5uETyUckWtu0Lj7KjFZAAAAA/kW1RUyO1EHwzw6aaOden_jmsGUKsiXTShjgETHDzYzw</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr"/>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Développeur back-end Sylius senior (H/F)</t>
+          <t>Conditions d'utilisation</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-3434f85229218170&amp;mo=r&amp;ad=-6NYlbfkN0B72_YPdqDh7vgg0I6GbYttYmNh7huT73r8xnUG2kqUIJwlLLS9EXZcLo5fXTL6gbyBrGyF35WdCR-AOudUOQcw9WHPZvo5oyDWkmTTEGHguAqA6929W2hxUSav-tf-XVYHt374Z59CiREnr47Agef2pAkf4GlPG9mK7BcXLcdGRUG4Iuxc3OabdOOX1dHb9jgPBk0vyWchPAxQSgFuELfJ_f_VOJsBlOJBwMm7-BLqkCrwZiDOGWLeDRa-ffrJ2jNQUawGu8S-tSsb1fhgL2DwNElMylAcAxwmZCRPn77FD26alzj3hqGGPqXleyWU5Rul77ZJASayJVwZYgMSBUnkMHvwFO2s7avKNTZZxGi2RC7ysEymeK92JQJuV90dZ8qbfnOmJoHIhLAeJ5PRL2LqBWjnoTo_TWKA99oZ_kqrrTEUF2Nq4VD5ACWyWKwQlfqxkBRWJcecWfLlZIt8l-Kbvsy0xBOo_u86hfO-dmVqTP-1brK1G5V0LRrKwplUrjgnGUrmIDJs7_diMrlbJfg7mQ1jGGGMIrgI1-ClCmhRyeJU2suHpwKvvOQa38dHypJt8UU85vnxePLkPEAe35NFhd4rUWcUedD6hl2ULAoASK-MeK149ziTQvqPy1c0Ehg8e9TgqjAnBR6-KZ3DBBPc6TY5BVqfl-KRICF0Gng4nLfCkPbLverDp74Iq3jF7nPI_oCLRJ_0C9BDsq_y-Fr15ty8L31wQWz7Uz4QnlURTckf6JEiLN1uEjxhT1I4wXdsseEnJksWHQ%3D%3D&amp;rm=2&amp;xkcb=SoDy6_M2eFuXPD1eJh0LbzkdCdPP&amp;jsa=7901&amp;camk=C3EPSzFlQw9ISSB8G8uPMQ%3D%3D</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2Myw7CIBBF_2XcmkJ9Aolx7d4fqDCUBiiVDiam6b9LNy7vOTl3gQIKHNE0K8ZsbobRIJpGp8gC9l24u3CzeUdphj1EUAt0Wqcy0sPU8CSlOAouL1XqMGj_dDmV3lVFueCffifcEOa43ZCvo_WH8-fNX1dP1gvewrr-ALn9SoqNAAAA/ulGitdpRG6-tZ8pccyrPFSeZfwN7ufnIBapuqRNJiEA</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Informaticien / Informatique industrielle (H/F)</t>
+          <t>Connexion</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-f12f49a0acd1aad0&amp;mo=r&amp;ad=-6NYlbfkN0CtHDpfysi4zSzUkFyX9EIqt90NLsWw1CcrCE8iJy70OcSBd0gBo5Xo4ffHQcK7A5B5YyK_LKqmmUdTCh3D6g8sh2Ir1irigzN4q27cKt2P4o2oJnE9lhu5FJSg9dDRRh8Azxr8B0VfbLM6oXDGSRNgqNs7Zbj1AD2Vt0pS54SEkGLW2Av1rUijVp-OfEoiA_DUujWg8JviCiEWf6cX7qpx-S-0TbeF8IGd2gSRmfM7EuVGHsJUFel7mJheJBnCv7Y1tKyEMArnjW7DLKnDImMp77h-_UX9O1ywYm9GQx5Rvhii7ypaeb8_lX7oABc9RCJl8Pd0fO_DngLEtFIFZTyRXKKeKkcF9L-24ogCyxistm1C-YLjzvV2EehqpXg9lJkBDxbrd7NTGmsERTL_mvUqC_GaL6kx5bq_Xn2eZ8SinB3erGdGu_NTkVodyuWeZWdonsQAEgxxCYHavh1KjQcgxGwtRFYHqxZA_39mkJVZ0da6l5aRnhm4QlfU4oxrV56Rj4frEgEFDZNGV5ZYhx-kG_7Js8UKIXNv8wd9AOpSsKvZH1QIiQitG-_7LTTPlKbEZO8xm2PRL23ZxebiFbdvGP_nwUMG8mjjukCCrjpZQSyLwEtEsIGkfYgjdRVfGQLnUN4nl3nw2ZLysyccdb3u_BR2LS5l8kZJltNgQOh1C50lt2hBWhqdddc0jjscA-puHBpp0vv81ZVuy8pMjKd6Ruk-22apBX7GqKJHUshRR1n7OSFqJPfcMFgsrHZJLIXnRvA8uF6NYA%3D%3D&amp;rm=2&amp;xkcb=SoBG6_M2eFuXMm1eJh0MbzkdCdPP&amp;jsa=7959&amp;camk=C3EPSzFlQw9qAyu0gh7UJg%3D%3D</t>
+          <t>https://secure.indeed.com/account/login?continue=https%3A%2F%2Ffr.indeed.com%2F&amp;from=jobi2a_multijob-fr-FR_email&amp;tk=1k25j6726l2fh801&amp;co=FR&amp;hl=fr</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Administrateur·rice des Applicatifs et du Référentiel - H/F</t>
+          <t>Développeur back-end Sylius senior (H/F)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-e7fa06f4499f5f07&amp;mo=r&amp;ad=-6NYlbfkN0Auhn5wMOaYr5_rtzNsnWpG4wqcT1I7wsJHeGMspvqAHskEPRkNoOS_D4AouJfIif0IJcSAplHaOChrX4ckjXixKA-cIr3B9NruW2QTnx-W5zOeqkvRYjmumTLByuzdZigjlJ_dlqvtGuRJ1LvDlvoAYFq7_nXhcC0RUNqNwXaZfzAfamqPXchkQDQf0dJThLtZhF3kMwDobj95ncoPWdkjufMBrlcA6tIaq5K4bSN7f4m-duDvelMGNivpEmcknroKH5nLpvnX8WsQHbARVX6Esd0PXpIGHxyGyhL1h_rfYlNXKEIw-14toPGhNvNc1thtx0j-AQlWxTsR6TD-2A35NLm9d2onhBSr-DJdtCqInAKX-3q10smjsCoVyMpEn6zyi8YtaFTae63ZG8MKUejZ83ZJCf3Q_Z9f49beNOetv_kfeODHy7sW-JOolAhlyRLCBEliWvQhjIwXDdegxuEd45aS48VfoEsBB9rMzBmC2SoXRHlgsKgOFgNkGnrQxM6Be0yEOwLBWJM71Ck1kTWFZnWfyWFK0y5iXiv-ffZTPSvx-ug0-G-St4mai0ckkjgwLB-OSQ4ij2fLm6HHfJasm7Gr10E2gofz3E8vue_w8p4LArYq9YO7F9ndUarryGd4IvgWyxfRXb3_E3iC0cd8n0imH71bwIlJgMZ0LWPc_Xymp0dgGFVesvKYyihjdYrlk0ofPCQtpIrvLgzIESzPiyJF0HODs6ocOhplFQ_lUgqPWL_aaZXvz9Ey25pvsjbG_kbY2Zspw9QRDPfEXnd3oJ9IxEgL5cuGd1vFw3KQZaEwOnlEq2kHrlam8M74WBCKGLztKZ2hnQ%3D%3D&amp;rm=2&amp;xkcb=SoDX6_M2eFuXMF1eJh0rbzkdCdPP&amp;jsa=8017&amp;camk=UoKtGZLa3XLkAB9aeqAIlg%3D%3D</t>
+          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-3434f85229218170&amp;mo=r&amp;ad=-6NYlbfkN0B72_YPdqDh7vgg0I6GbYttYmNh7huT73r8xnUG2kqUIJwlLLS9EXZcLo5fXTL6gbyBrGyF35WdCR-AOudUOQcw9WHPZvo5oyDWkmTTEGHguAqA6929W2hxUSav-tf-XVYHt374Z59CiREnr47Agef2pAkf4GlPG9mK7BcXLcdGRUG4Iuxc3OabdOOX1dHb9jgPBk0vyWchPAxQSgFuELfJ_f_VOJsBlOJBwMm7-BLqkCrwZiDOGWLeDRa-ffrJ2jNQUawGu8S-tSsb1fhgL2DwNElMylAcAxwmZCRPn77FD26alzj3hqGGPqXleyWU5Rul77ZJASayJVwZYgMSBUnkMHvwFO2s7avKNTZZxGi2RC7ysEymeK92JQJuV90dZ8qbfnOmJoHIhLAeJ5PRL2LqBWjnoTo_TWKA99oZ_kqrrTEUF2Nq4VD5ACWyWKwQlfqxkBRWJcecWfLlZIt8l-Kbvsy0xBOo_u86hfO-dmVqTP-1brK1G5V0LRrKwplUrjgnGUrmIDJs7_diMrlbJfg7mQ1jGGGMIrgI1-ClCmhRyeJU2suHpwKvvOQa38dHypJt8UU85vnxePLkPEAe35NFhd4rUWcUedD6hl2ULAoASK-MeK149ziTQvqPy1c0Ehg8e9TgqjAnBR6-KZ3DBBPc6TY5BVqfl-KRICF0Gng4nLfCkPbLverDp74Iq3jF7nPI_oCLRJ_0C9BDsq_y-Fr15ty8L31wQWz7Uz4QnlURTckf6JEiLN1uEjxhT1I4wXdsseEnJksWHQ%3D%3D&amp;rm=2&amp;xkcb=SoDy6_M2eFuXPD1eJh0LbzkdCdPP&amp;jsa=7901&amp;camk=C3EPSzFlQw9ISSB8G8uPMQ%3D%3D</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Administrateur Technique H/F</t>
+          <t>Informaticien / Informatique industrielle (H/F)</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-93eb2fcfbcdd4897&amp;mo=r&amp;ad=-6NYlbfkN0Auhn5wMOaYr5_rtzNsnWpG4wqcT1I7wsJHeGMspvqAHskEPRkNoOS_D4AouJfIif2B3u6e8ulFbHVvkp3ES5PkEhWdTMOGV15R0U7eQ5VLKQLi2tHzYAWenu5zAfigEH1z_xztNnWOLcsxzvxM05dZIf3pYA6_OY4YRPk_bDpC74gyWYmfj0I2HkdwMyd0NZfnnWmhJ06rRHL_b-7rcxY28-4yqEGF8ILOPMIrtNHx9LOK3tmObFCnjqIQEEkY1eHR0m0PL8UAr880zj9y8Nkf0GebTImMnKtoJ_9EYhMRYeubWJgWwBhWVG0Cz2AFI8XgBenUJLQsXCDGdoOTYdd9C2ASeznreO6IE1Xcvj3Wa7-Qey3OcX-Wu7i-_uBxiVwU78AAZji49KfeKlsGGScRD89upZbA4XTXj0MZz8B2FDekcypt5ckjE4UDeA9p0FdTD447FFLd-nUghyPZSs5s7dYSz_WfT-XmRYD6rKcXDOHohzPQUuHHZ_dZevDjX3qSIiuY2l61By0OqWifFL7l9T7f3OtPGyu2b3x217DhWNwR1g_L5OiICbW5-rsEpB5U5kijz1QfpE9UFiTx1P1Sa0c6f-jqRHiflLHOPnRwc-dXVaYy48ejPPYpDZ32-2IT105WFEJnuDnLZjw-PLh4HxmKIrbut7DkGcrzrAlIG6Tqu5JNtVbxL7N1UOR5-7a_M1O3UD_qCrcCPlylE169l0BO7r8nfIW2gm2lfU0PnKmr3lq8Y1tKKttrqyaws4FyGBtpdB1JlsFTTmehgNPiJwjoLpnheDo%3D&amp;rm=2&amp;xkcb=SoCV6_M2eFuXNp1eJh0BbzkdCdPP&amp;jsa=8105&amp;camk=UoKtGZLa3XLkAB9aeqAIlg%3D%3D</t>
+          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-f12f49a0acd1aad0&amp;mo=r&amp;ad=-6NYlbfkN0CtHDpfysi4zSzUkFyX9EIqt90NLsWw1CcrCE8iJy70OcSBd0gBo5Xo4ffHQcK7A5B5YyK_LKqmmUdTCh3D6g8sh2Ir1irigzN4q27cKt2P4o2oJnE9lhu5FJSg9dDRRh8Azxr8B0VfbLM6oXDGSRNgqNs7Zbj1AD2Vt0pS54SEkGLW2Av1rUijVp-OfEoiA_DUujWg8JviCiEWf6cX7qpx-S-0TbeF8IGd2gSRmfM7EuVGHsJUFel7mJheJBnCv7Y1tKyEMArnjW7DLKnDImMp77h-_UX9O1ywYm9GQx5Rvhii7ypaeb8_lX7oABc9RCJl8Pd0fO_DngLEtFIFZTyRXKKeKkcF9L-24ogCyxistm1C-YLjzvV2EehqpXg9lJkBDxbrd7NTGmsERTL_mvUqC_GaL6kx5bq_Xn2eZ8SinB3erGdGu_NTkVodyuWeZWdonsQAEgxxCYHavh1KjQcgxGwtRFYHqxZA_39mkJVZ0da6l5aRnhm4QlfU4oxrV56Rj4frEgEFDZNGV5ZYhx-kG_7Js8UKIXNv8wd9AOpSsKvZH1QIiQitG-_7LTTPlKbEZO8xm2PRL23ZxebiFbdvGP_nwUMG8mjjukCCrjpZQSyLwEtEsIGkfYgjdRVfGQLnUN4nl3nw2ZLysyccdb3u_BR2LS5l8kZJltNgQOh1C50lt2hBWhqdddc0jjscA-puHBpp0vv81ZVuy8pMjKd6Ruk-22apBX7GqKJHUshRR1n7OSFqJPfcMFgsrHZJLIXnRvA8uF6NYA%3D%3D&amp;rm=2&amp;xkcb=SoBG6_M2eFuXMm1eJh0MbzkdCdPP&amp;jsa=7959&amp;camk=C3EPSzFlQw9qAyu0gh7UJg%3D%3D</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr"/>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Technicien Datacenter H/F</t>
+          <t>Administrateur·rice des Applicatifs et du Référentiel - H/F</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-f5fba648d62dfa24&amp;mo=r&amp;ad=-6NYlbfkN0A_Y3vTaZcLmRryC3Yh0qbVCQ9n1Sys9lQxhKpzANCmp6B5ftKDRYN08izJ8lHLmedhSBW6Qgesvv5hOdfUY8ZV7_NsyJjj1J2_9-CRRTg0Z2Nz5m4YbeUS2OMGMkM0VHWysfFp0uXwwc0lPmNfoGRw1ZiGyboZ4rTJK-eQ11PLow8t_JY-gblgoPefGf4MECUJGIdl8P2PLdumCHdpydoWhpAteG_G3q2ok1CY0zzYYclN4zTRs_75ZXCOPwBDVpNJlO1boY8NAi4tgSv5D5gP0O7BBg_01RCdoMb_Z-kSwUR5wkZv8jwqiQujZnHm0niFLwAs04AVUIM5WE76Hy2_v9qE7PK-J6qaomHtHT203JGtpAgrniEUsyvmpxe4ponZNlwdpEsweFn78XIeCPCq0iQVeOpj9GptKwqBtGlg7kmIn0IpBCOKS23wAX307C7Y_Y_3RhMd9rU84CJTJSjgHkeCtkjDX4-Z2E7KWWFpg3gZy6b5hc6QOTj_90HPGL08VZGflVyw0MkKnoQqs_iBZqNc-T8plghSzniK00txpSFk6F80iJpcRz-h_YIRb4lwFRZLcArsfTnJb3fbqd4km0LkrP5MXRrUBE_L-P_-E4wgp4jI0onDXfDhRfXd1T1UF31YgPt2Cw44bIDYb8rJNIL69gJWtZQc7vmuDONI2dFlEu3fhODJdzjb8YIkwJ7sUv3cp_7b53JkaD8nnzbbQ-7LJi5Io2J2UENIoHrtAlPvynPq7TnE&amp;rm=2&amp;xkcb=SoBc6_M2eFuXKV1eJh0abzkdCdPP&amp;jsa=8241&amp;camk=C3EPSzFlQw8KsRdjpoVIQw%3D%3D</t>
+          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-e7fa06f4499f5f07&amp;mo=r&amp;ad=-6NYlbfkN0Auhn5wMOaYr5_rtzNsnWpG4wqcT1I7wsJHeGMspvqAHskEPRkNoOS_D4AouJfIif0IJcSAplHaOChrX4ckjXixKA-cIr3B9NruW2QTnx-W5zOeqkvRYjmumTLByuzdZigjlJ_dlqvtGuRJ1LvDlvoAYFq7_nXhcC0RUNqNwXaZfzAfamqPXchkQDQf0dJThLtZhF3kMwDobj95ncoPWdkjufMBrlcA6tIaq5K4bSN7f4m-duDvelMGNivpEmcknroKH5nLpvnX8WsQHbARVX6Esd0PXpIGHxyGyhL1h_rfYlNXKEIw-14toPGhNvNc1thtx0j-AQlWxTsR6TD-2A35NLm9d2onhBSr-DJdtCqInAKX-3q10smjsCoVyMpEn6zyi8YtaFTae63ZG8MKUejZ83ZJCf3Q_Z9f49beNOetv_kfeODHy7sW-JOolAhlyRLCBEliWvQhjIwXDdegxuEd45aS48VfoEsBB9rMzBmC2SoXRHlgsKgOFgNkGnrQxM6Be0yEOwLBWJM71Ck1kTWFZnWfyWFK0y5iXiv-ffZTPSvx-ug0-G-St4mai0ckkjgwLB-OSQ4ij2fLm6HHfJasm7Gr10E2gofz3E8vue_w8p4LArYq9YO7F9ndUarryGd4IvgWyxfRXb3_E3iC0cd8n0imH71bwIlJgMZ0LWPc_Xymp0dgGFVesvKYyihjdYrlk0ofPCQtpIrvLgzIESzPiyJF0HODs6ocOhplFQ_lUgqPWL_aaZXvz9Ey25pvsjbG_kbY2Zspw9QRDPfEXnd3oJ9IxEgL5cuGd1vFw3KQZaEwOnlEq2kHrlam8M74WBCKGLztKZ2hnQ%3D%3D&amp;rm=2&amp;xkcb=SoDX6_M2eFuXMF1eJh0rbzkdCdPP&amp;jsa=8017&amp;camk=UoKtGZLa3XLkAB9aeqAIlg%3D%3D</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Consultant stratégies IT et systèmes end-to-end - F/H (DSI/MSP)</t>
+          <t>Administrateur Technique H/F</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-119849681d2a8851&amp;mo=r&amp;ad=-6NYlbfkN0D4RVQlBwGREJrEUYTeBI5cK_LclF7BnZWESDe75fNy8zVHagq8e8VX0DHfLftANGuwDt7uSOreE05LZgGydVBjxPrCDAE8vYY1BpYpkuK-FiAvACYeLQQu7fwTpzrymhmm6fMtftiuSF47QkwFI3PbIPyypAeOSFb3ejO5lcs7ufwiJIUyUfgLpkAluTTe9y6Vqxa515sFq_sdPwRBU7sW-1DblcvfplF8l-bbyaQ3jtBuuUm0Ii2aHZodmQKFu30GQR7YGJFBfwdMkul-nerlkpWKE3-UK7VaKJTRSYAPGNcm_q_EtnLnWnQC5n96eEPDCRbkWOl0p0tkSucNwxchsh15MMBmR95ZyY8KccVLPjvJeJxu9Tvr-_dPbf5wfF06kOTbXobXHBAr019f83GELQNRpKkex4pDnvbf8TKuUj9dJ3NmT3twnb4drSuVky-IhwMestNlHjQuH7c-ufkwYz6AR4oCFS83nmyWz0X0m79bcD5gWAF6sWhTt2a3sYtC48GtV8U3EeAvyao9tIX2f-NbZazkiuYT3euXkqpubF9OEibOfo-FTq0mQx79y_1Gpx7IZb_lko1EM1J-qOoWsNA03H8C2tQgzdt2rJ5NuFHVW8pp51yNBBR6o3vAnPwCPqGAQa43v5EIGHQzft6IwW0O072MkX0Scq-nqL0mDvFxZs-9UWKRB_RQcpWjb49uEx8sD63WsoaeQK_qsuacny9ZWQZE2uGFuanLB5b7s5VFlfF38teouzlBoHee35xlLIfmOSQ6g75jqDex-_x-aFtQAVj-GqFYdwcvGw6VIl9E6FRHMxMRIj1e9s84bYGV0uk1gnA_o-v5HMivDghvjLwA7oCKMbf0UbUURPvXdZ_1-caWiVVZYE1nOILK2IvPAvGR4h--F780BdeKQ2-hK5a7HHBNAjkhTA7jHTJXaw%3D%3D&amp;rm=2&amp;xkcb=SoCS6_M2eFuXNL1eJh0obzkdCdPP&amp;jsa=8173&amp;camk=ethIe0s0hecvn9-NTlcNVg%3D%3D</t>
+          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-93eb2fcfbcdd4897&amp;mo=r&amp;ad=-6NYlbfkN0Auhn5wMOaYr5_rtzNsnWpG4wqcT1I7wsJHeGMspvqAHskEPRkNoOS_D4AouJfIif2B3u6e8ulFbHVvkp3ES5PkEhWdTMOGV15R0U7eQ5VLKQLi2tHzYAWenu5zAfigEH1z_xztNnWOLcsxzvxM05dZIf3pYA6_OY4YRPk_bDpC74gyWYmfj0I2HkdwMyd0NZfnnWmhJ06rRHL_b-7rcxY28-4yqEGF8ILOPMIrtNHx9LOK3tmObFCnjqIQEEkY1eHR0m0PL8UAr880zj9y8Nkf0GebTImMnKtoJ_9EYhMRYeubWJgWwBhWVG0Cz2AFI8XgBenUJLQsXCDGdoOTYdd9C2ASeznreO6IE1Xcvj3Wa7-Qey3OcX-Wu7i-_uBxiVwU78AAZji49KfeKlsGGScRD89upZbA4XTXj0MZz8B2FDekcypt5ckjE4UDeA9p0FdTD447FFLd-nUghyPZSs5s7dYSz_WfT-XmRYD6rKcXDOHohzPQUuHHZ_dZevDjX3qSIiuY2l61By0OqWifFL7l9T7f3OtPGyu2b3x217DhWNwR1g_L5OiICbW5-rsEpB5U5kijz1QfpE9UFiTx1P1Sa0c6f-jqRHiflLHOPnRwc-dXVaYy48ejPPYpDZ32-2IT105WFEJnuDnLZjw-PLh4HxmKIrbut7DkGcrzrAlIG6Tqu5JNtVbxL7N1UOR5-7a_M1O3UD_qCrcCPlylE169l0BO7r8nfIW2gm2lfU0PnKmr3lq8Y1tKKttrqyaws4FyGBtpdB1JlsFTTmehgNPiJwjoLpnheDo%3D&amp;rm=2&amp;xkcb=SoCV6_M2eFuXNp1eJh0BbzkdCdPP&amp;jsa=8105&amp;camk=UoKtGZLa3XLkAB9aeqAIlg%3D%3D</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr"/>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Afficher plus d'emplois</t>
+          <t>Technicien Datacenter H/F</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>https://fr.indeed.com/?co=FR&amp;utm_campaign=job_alerts&amp;utm_medium=email&amp;utm_source=jobseeker_emails&amp;from=jobi2a_multijob-fr-FR_email&amp;tk=1k25j6726l2fh801</t>
+          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-f5fba648d62dfa24&amp;mo=r&amp;ad=-6NYlbfkN0A_Y3vTaZcLmRryC3Yh0qbVCQ9n1Sys9lQxhKpzANCmp6B5ftKDRYN08izJ8lHLmedhSBW6Qgesvv5hOdfUY8ZV7_NsyJjj1J2_9-CRRTg0Z2Nz5m4YbeUS2OMGMkM0VHWysfFp0uXwwc0lPmNfoGRw1ZiGyboZ4rTJK-eQ11PLow8t_JY-gblgoPefGf4MECUJGIdl8P2PLdumCHdpydoWhpAteG_G3q2ok1CY0zzYYclN4zTRs_75ZXCOPwBDVpNJlO1boY8NAi4tgSv5D5gP0O7BBg_01RCdoMb_Z-kSwUR5wkZv8jwqiQujZnHm0niFLwAs04AVUIM5WE76Hy2_v9qE7PK-J6qaomHtHT203JGtpAgrniEUsyvmpxe4ponZNlwdpEsweFn78XIeCPCq0iQVeOpj9GptKwqBtGlg7kmIn0IpBCOKS23wAX307C7Y_Y_3RhMd9rU84CJTJSjgHkeCtkjDX4-Z2E7KWWFpg3gZy6b5hc6QOTj_90HPGL08VZGflVyw0MkKnoQqs_iBZqNc-T8plghSzniK00txpSFk6F80iJpcRz-h_YIRb4lwFRZLcArsfTnJb3fbqd4km0LkrP5MXRrUBE_L-P_-E4wgp4jI0onDXfDhRfXd1T1UF31YgPt2Cw44bIDYb8rJNIL69gJWtZQc7vmuDONI2dFlEu3fhODJdzjb8YIkwJ7sUv3cp_7b53JkaD8nnzbbQ-7LJi5Io2J2UENIoHrtAlPvynPq7TnE&amp;rm=2&amp;xkcb=SoBc6_M2eFuXKV1eJh0abzkdCdPP&amp;jsa=8241&amp;camk=C3EPSzFlQw8KsRdjpoVIQw%3D%3D</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Suspendre ces emails</t>
+          <t>Consultant stratégies IT et systèmes end-to-end - F/H (DSI/MSP)</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>https://match.indeed.com/invitations/pause?tk=1k25j6726l2fh801&amp;info=AAAAAccRgLRXW2NP5OliVxo7PvQRNGXH32Uq6zV0zBBfwodA3w5OEbljx9CabEKae2J3SSNOtlJh0EnaPe9lpnj47LL2tg_kt5TadWKWqNuSLdInrwzOdE3LqPt2tR1sx27Cu98PQMsHqDno4KbTaSf9_Ubsmx6j6_9S5kmHord6oqzxaiEonEaK45leWuNCl7xxSGRCUZ5C</t>
+          <t>https://fr.indeed.com/pagead/clk/dl?from=jobi2a_multijob-fr-FR_email&amp;jrtk=5-cmh1-1-1k25j66e4m6fb800-119849681d2a8851&amp;mo=r&amp;ad=-6NYlbfkN0D4RVQlBwGREJrEUYTeBI5cK_LclF7BnZWESDe75fNy8zVHagq8e8VX0DHfLftANGuwDt7uSOreE05LZgGydVBjxPrCDAE8vYY1BpYpkuK-FiAvACYeLQQu7fwTpzrymhmm6fMtftiuSF47QkwFI3PbIPyypAeOSFb3ejO5lcs7ufwiJIUyUfgLpkAluTTe9y6Vqxa515sFq_sdPwRBU7sW-1DblcvfplF8l-bbyaQ3jtBuuUm0Ii2aHZodmQKFu30GQR7YGJFBfwdMkul-nerlkpWKE3-UK7VaKJTRSYAPGNcm_q_EtnLnWnQC5n96eEPDCRbkWOl0p0tkSucNwxchsh15MMBmR95ZyY8KccVLPjvJeJxu9Tvr-_dPbf5wfF06kOTbXobXHBAr019f83GELQNRpKkex4pDnvbf8TKuUj9dJ3NmT3twnb4drSuVky-IhwMestNlHjQuH7c-ufkwYz6AR4oCFS83nmyWz0X0m79bcD5gWAF6sWhTt2a3sYtC48GtV8U3EeAvyao9tIX2f-NbZazkiuYT3euXkqpubF9OEibOfo-FTq0mQx79y_1Gpx7IZb_lko1EM1J-qOoWsNA03H8C2tQgzdt2rJ5NuFHVW8pp51yNBBR6o3vAnPwCPqGAQa43v5EIGHQzft6IwW0O072MkX0Scq-nqL0mDvFxZs-9UWKRB_RQcpWjb49uEx8sD63WsoaeQK_qsuacny9ZWQZE2uGFuanLB5b7s5VFlfF38teouzlBoHee35xlLIfmOSQ6g75jqDex-_x-aFtQAVj-GqFYdwcvGw6VIl9E6FRHMxMRIj1e9s84bYGV0uk1gnA_o-v5HMivDghvjLwA7oCKMbf0UbUURPvXdZ_1-caWiVVZYE1nOILK2IvPAvGR4h--F780BdeKQ2-hK5a7HHBNAjkhTA7jHTJXaw%3D%3D&amp;rm=2&amp;xkcb=SoCS6_M2eFuXNL1eJh0obzkdCdPP&amp;jsa=8173&amp;camk=ethIe0s0hecvn9-NTlcNVg%3D%3D</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Voir l'emploi</t>
+          <t>Afficher plus d'emplois</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32UWaurSBRG_0ug89Teo-V8IDQOMRo1MTHGmBdxHsoppSbq5f739nZDPza1oWB9RW0oaq-fm3HzvcmHoeu_v75S9KNo4iSJf0Rt_dUFWRLEX1EF_0pRW-_KNixA4K9bHQxRjqUIU65-UgdFtS3RAHc0FtU5ga0LArqkeRJ1KQAczmApHUQJSbNsSoUxwbLbut2hbRDvMObkVWEKT7jEoORytDrulLcZSUkgI51GPbGc1U61LhrGvautQAi5_FrhT1GGo_hiSt9Cvuk8YFy5KVdO1bAfHoRjnVhfJI43_eNKjXZYIvcVEN5hQVOm86Tjynvh2dSP8t23JGmYbxa9ut7WQiZhrzWWvgs_P1OtnSs6PBTweXNk6ooKhvZ95w1GxTKcWY1VNxRs8YLpmWe5iuCfe1k6XgZZCs9Wig6P-2gh-na27smp8iQtJlBjp2_NRL1X7uX91WVMmqrVwNWF6uM4XaVUSESXE-vJPaRZfApeyyJWT-JCppLaz9fHQMXGUeG8ErcqkSP9GhNqjVr7R3ola-0Fr88zxnR8jnfeOBHHnOsJKlEvHkzhYQGv0eZuzGI5tKFZMy8lxl6j877MA5FU6yYF2SOfMrpBnmwdjw4mQ4LRQKQAKRM1h3WNuGhOCtUjDziZcba8ccZmjX8gp-wOj7LvVAN_2loZ68WIQH1bb0wl7TWb_JQKAf5O4MlQold2ul489lXl0MuCkGjsbsZJTr-pmDmF2gcUwnGPX0tDY82DnScsZzMNBRwzzD0Ffyrz82yfO2VBZyrgyqs44j7T95NEtHT0QsRIikrIwwK1z7P5mbS79LHO9edF40CC5DglsDYuzvqTOsm7V3io6w3MvUzF3PUZXXqfGWTfBO2Bymkr9h2OkHPfKB01fbziwVx0lkuTRFv0RJVoe3p5zUfgYSUmfqbPx7iSfIpcRuvpdrK4pPVNmElrcjkYCRU4hV06h2PwJJn2GgLv_ox4sODdTW0-tm8TLXNrXMm-Drl398sTO_U4QsjI3yF99C-ce-uTyh8Mgb8Z5IGm19HDAAEVNzuc_fcMleBxKSYznT0ubYETmpGU4ltU78B2glG4s1t5z_gmSJQxqBnQcDSuhguMpdiytmUf7Fie57dRUMOdRO4te1Gqy4eDT7NyrIqqG-EPUl5r8-em3nz_3ARR1I7NoMWrPyie50gO55k1DLLs2Ib_YAIHNANYhgL4GkRVEcFbjtoxy9dwQGPyH527ZEXvIvmsdlnpb9-s4H-Msx4a4O8e_6pmbOGQQg4nNr9-_Q31N98e1AQAAA/dbSJlXsaIJxnvs3HrpvfST6juVTaQ89LxI-hdc_XvF4</t>
+          <t>https://fr.indeed.com/?co=FR&amp;utm_campaign=job_alerts&amp;utm_medium=email&amp;utm_source=jobseeker_emails&amp;from=jobi2a_multijob-fr-FR_email&amp;tk=1k25j6726l2fh801</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr"/>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Ne correspond pas</t>
+          <t>Suspendre ces emails</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QzW6jMBRG38WLWY0bMH8mUlVBB5J00qRNJ0raDTJgwBBjYkxJqfru42Yxi7mbK51zpe_q-wQDmINKqa6fz2acqKy6YW1OaX6TCT5j7TtTRDHR9rNWKMhaRSXtFc3vVHNrNsipHX8QjSoabJg_WFuI2-B7jv4It8HZOvbPm3ijui54OqMdfTTDS1x5SVz_jkaYRHWyPrwE8eV06E5PUTmpwxl63dZWD-uMvaYJ3o_rabFYnyO_IgiaK14z3h0RXqRp-RLygJLc4OFxaZfvdjFIvAmf5Xi4j7ZT6BQWujjj3q8nRSzV85HBWkQX_xfef7iRx-ru7S3eruRjUMSh_oLvpsq1c-teWt6wjEaMl-An4GD-CUiWiaFVq1yXZfs-trDhu1qSsnwQ6RWbBnJc5Lk2MrTITixr_lRSDGWlpZID_Uc_OqpRSnJ47VvzQgodA2qRMkQSva4CFhLGu4Rywk76SDXfKf9VDr6-_gIJZezuwwEAAA/QBWqSKZmsUqvYYtDXQkWhy4NaI3_XEal4N9d_Em52QY</t>
+          <t>https://match.indeed.com/invitations/pause?tk=1k25j6726l2fh801&amp;info=AAAAAccRgLRXW2NP5OliVxo7PvQRNGXH32Uq6zV0zBBfwodA3w5OEbljx9CabEKae2J3SSNOtlJh0EnaPe9lpnj47LL2tg_kt5TadWKWqNuSLdInrwzOdE3LqPt2tR1sx27Cu98PQMsHqDno4KbTaSf9_Ubsmx6j6_9S5kmHord6oqzxaiEonEaK45leWuNCl7xxSGRCUZ5C</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr"/>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Modifier le profil</t>
+          <t>Voir l'emploi</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_0sGp8av1mIE6SZ0le4S89HEJEbim6GI_70ZSqeDu4e7O1BEHVIA294VxRa81FbkeuVC8Jx595DBu37xs67plMRRYArLgIdxEo5qmzHfD2OmbC8DuiCHugNRxnxc4clT9Y2Q9tqW5J5CZjUzLxV8fKsUQYji7342kazd0QBYpvGZMoMF14B_pxIJJiGVqZulIdEbkKYtK3SeX2dPm7DFAAAA/sqwWb6EByg1YW25uIO5FgqakEkaKB7FrpfwrTP-GhBo</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32UWaurSBRG_0ug89Teo-V8IDQOMRo1MTHGmBdxHsoppSbq5f739nZDPza1oWB9RW0oaq-fm3HzvcmHoeu_v75S9KNo4iSJf0Rt_dUFWRLEX1EF_0pRW-_KNixA4K9bHQxRjqUIU65-UgdFtS3RAHc0FtU5ga0LArqkeRJ1KQAczmApHUQJSbNsSoUxwbLbut2hbRDvMObkVWEKT7jEoORytDrulLcZSUkgI51GPbGc1U61LhrGvautQAi5_FrhT1GGo_hiSt9Cvuk8YFy5KVdO1bAfHoRjnVhfJI43_eNKjXZYIvcVEN5hQVOm86Tjynvh2dSP8t23JGmYbxa9ut7WQiZhrzWWvgs_P1OtnSs6PBTweXNk6ooKhvZ95w1GxTKcWY1VNxRs8YLpmWe5iuCfe1k6XgZZCs9Wig6P-2gh-na27smp8iQtJlBjp2_NRL1X7uX91WVMmqrVwNWF6uM4XaVUSESXE-vJPaRZfApeyyJWT-JCppLaz9fHQMXGUeG8ErcqkSP9GhNqjVr7R3ola-0Fr88zxnR8jnfeOBHHnOsJKlEvHkzhYQGv0eZuzGI5tKFZMy8lxl6j877MA5FU6yYF2SOfMrpBnmwdjw4mQ4LRQKQAKRM1h3WNuGhOCtUjDziZcba8ccZmjX8gp-wOj7LvVAN_2loZ68WIQH1bb0wl7TWb_JQKAf5O4MlQold2ul489lXl0MuCkGjsbsZJTr-pmDmF2gcUwnGPX0tDY82DnScsZzMNBRwzzD0Ffyrz82yfO2VBZyrgyqs44j7T95NEtHT0QsRIikrIwwK1z7P5mbS79LHO9edF40CC5DglsDYuzvqTOsm7V3io6w3MvUzF3PUZXXqfGWTfBO2Bymkr9h2OkHPfKB01fbziwVx0lkuTRFv0RJVoe3p5zUfgYSUmfqbPx7iSfIpcRuvpdrK4pPVNmElrcjkYCRU4hV06h2PwJJn2GgLv_ox4sODdTW0-tm8TLXNrXMm-Drl398sTO_U4QsjI3yF99C-ce-uTyh8Mgb8Z5IGm19HDAAEVNzuc_fcMleBxKSYznT0ubYETmpGU4ltU78B2glG4s1t5z_gmSJQxqBnQcDSuhguMpdiytmUf7Fie57dRUMOdRO4te1Gqy4eDT7NyrIqqG-EPUl5r8-em3nz_3ARR1I7NoMWrPyie50gO55k1DLLs2Ib_YAIHNANYhgL4GkRVEcFbjtoxy9dwQGPyH527ZEXvIvmsdlnpb9-s4H-Msx4a4O8e_6pmbOGQQg4nNr9-_Q31N98e1AQAAA/dbSJlXsaIJxnvs3HrpvfST6juVTaQ89LxI-hdc_XvF4</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr"/>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Suspendre ces emails</t>
+          <t>Ne correspond pas</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qy26CQABF_2UWXRWRlwwmpgELaqviowbqhiDPAQcGmBHE9N9Lu-iid3fP3dycB2BgClJKSTPleezTIB2hIoyicBSUmEfFDVGforJoeOKzJnqh-UzIRSVTNFbmNM7hWHhCRVzO9J-4WsvZeiW5zX5rbSkh-q4SD9FGMDorVT0rezdbzjMzb-0cdau7OuS6M5OeOhWnElumb-sAfV48eGrX_WKxrkwt9UVOWOEMYeKKcHG5JEcD65EfjrHhLuXkJseshltjX7fO3LR7Q4klsVPak5b11Jdog1vEZaXZaa_wdJ-YKsrI-WzZq3qjx5YxvMCHPp3IoTSvJZUtzRbCJXgGGEwfwA-CkhV0FQ6OZE2DEhxrk2EMrijIP9K6ZEk6TLRm0R-9k2hAv7IGRvOh_BcGvr6-AUw9xMp4AQAA/kLUc35e8ipAmsezCvRjIlG4nggjhWzGKNiVbw_w1q5E</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QzW6jMBRG38WLWY0bMH8mUlVBB5J00qRNJ0raDTJgwBBjYkxJqfru42Yxi7mbK51zpe_q-wQDmINKqa6fz2acqKy6YW1OaX6TCT5j7TtTRDHR9rNWKMhaRSXtFc3vVHNrNsipHX8QjSoabJg_WFuI2-B7jv4It8HZOvbPm3ijui54OqMdfTTDS1x5SVz_jkaYRHWyPrwE8eV06E5PUTmpwxl63dZWD-uMvaYJ3o_rabFYnyO_IgiaK14z3h0RXqRp-RLygJLc4OFxaZfvdjFIvAmf5Xi4j7ZT6BQWujjj3q8nRSzV85HBWkQX_xfef7iRx-ru7S3eruRjUMSh_oLvpsq1c-teWt6wjEaMl-An4GD-CUiWiaFVq1yXZfs-trDhu1qSsnwQ6RWbBnJc5Lk2MrTITixr_lRSDGWlpZID_Uc_OqpRSnJ47VvzQgodA2qRMkQSva4CFhLGu4Rywk76SDXfKf9VDr6-_gIJZezuwwEAAA/QBWqSKZmsUqvYYtDXQkWhy4NaI3_XEal4N9d_Em52QY</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr"/>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Centre d'aide</t>
+          <t>Modifier le profil</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ6CMBBF7zJrQ0HFtE2Ma_degExbiwXalJkFIdzdWRiX_728vwODhUhUVqvUyqXkSs24OO9dg3lWEVWojzjdQ4UTzGB3GBAzL_R0Ul6N0RfdmptInEZMr1gzv6Moquz_dCte0O9fKCWZXTr3n95wThSSbjs4ji80zklxkAAAAA/ZGLmCAo0WH_W7lRfc7eTjaboRPu99mdg_ATedGSl06k</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_0sGp8av1mIE6SZ0le4S89HEJEbim6GI_70ZSqeDu4e7O1BEHVIA294VxRa81FbkeuVC8Jx595DBu37xs67plMRRYArLgIdxEo5qmzHfD2OmbC8DuiCHugNRxnxc4clT9Y2Q9tqW5J5CZjUzLxV8fKsUQYji7342kazd0QBYpvGZMoMF14B_pxIJJiGVqZulIdEbkKYtK3SeX2dPm7DFAAAA/sqwWb6EByg1YW25uIO5FgqakEkaKB7FrpfwrTP-GhBo</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr"/>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Conditions d'utilisation</t>
+          <t>Suspendre ces emails</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ7CIBBF7zJuTWnVGiAxrt17gQaGUoFOQ4eFaXp36cblfy_vb1BAg2deVi2Ey800W0TbGEoi4jjEp48Pl09MK5whgd5gMIbKzC9bw5tS8ipbda_SxMmEt89URl8V54J_-l3wQJjTccOhji5c-k-vCgV2QbYd7PsPAoGg7o0AAAA/tS4HYPhGyDjc0--pJsMK92Qei0Fk_fzvewE9cKrsatg</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qy26CQABF_2UWXRWRlwwmpgELaqviowbqhiDPAQcGmBHE9N9Lu-iid3fP3dycB2BgClJKSTPleezTIB2hIoyicBSUmEfFDVGforJoeOKzJnqh-UzIRSVTNFbmNM7hWHhCRVzO9J-4WsvZeiW5zX5rbSkh-q4SD9FGMDorVT0rezdbzjMzb-0cdau7OuS6M5OeOhWnElumb-sAfV48eGrX_WKxrkwt9UVOWOEMYeKKcHG5JEcD65EfjrHhLuXkJseshltjX7fO3LR7Q4klsVPak5b11Jdog1vEZaXZaa_wdJ-YKsrI-WzZq3qjx5YxvMCHPp3IoTSvJZUtzRbCJXgGGEwfwA-CkhV0FQ6OZE2DEhxrk2EMrijIP9K6ZEk6TLRm0R-9k2hAv7IGRvOh_BcGvr6-AUw9xMp4AQAA/kLUc35e8ipAmsezCvRjIlG4nggjhWzGKNiVbw_w1q5E</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr"/>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Voir l'emploi</t>
+          <t>Centre d'aide</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32TWcurSBCG_0tgcjWezyUa-4MwxC1uUaNZNDfSrh33NRoP57-PZwbmcuiChuctqqDg-bkZN98bNAxN__31lXQ_XlUUx9GPsC6_GpjGMPoKi_yvpKvLQ1YHLxL661fCIURY0mGS7cclfBXbrBvyA42FJSKw9eUkndGA6pqEJFmcwfYhYHEWMvsdk9AA7rZlfei2MDpgjOEVQZIbOCdV3BWkLi1qLRwNI39zyfnMql2cl7mdOsZyGTI2nd_2XmXmW9QHSUg_osEMxDYBw3C-OsxlMHzEzEXylPOoaxZRhOLIoNv-7c0e18iFIzWCnkwXB9z1UZxpam7O3lUJqomiSNJJztaLiYiFkywJPDtlN4fmMvj2jcRvsiBxvFnTAMMNPaKNKgj0ktRAoyuK5UFPTU-e_WxhXN2PEkJ0dclNlXbE59hDYpLMZVJNHJSUxhNHS8dPHLra-_ImH83F9O-2O002y8h2eNvZIYFrEnYPjhpzXALtU6qfsyPLk98JttV1OCsntpPapMg8p8LSab56GLhm0qJ5TTUeOA7k73ofqmF6cemUp9772YcT2PmVXqDZ7k8zvyhFzLafu3CR2OwIxB1qQx9l3lMNAC43KuWwS2oiSsDy1kScV5Xvq5WAMLahJt1zBlHM20rrSnWhJB6veuWUrIiglz4NpGge0dbBXZOTJW5CfQ7myY8yVp4eAffaZ-K7UfNcDWcHsDEYslE6fU4WjgTKx85C32FEsczrPad-51hty42ByJ0CGz_ikS2MetWReSsGyDaUS90zlmDnUAl6FtFcT8pSa7tjf8vvrsy7UawVZICk6nqZbINn_DZ9xcv7lO0lrptVF4EMSdFoKkNBilcrI9vB5y4ule4Zci8IRLPQTBufBz6lo46KFyUb-UGp21ft5VJ3bDFaPgnCagkNZEH51OrrdHFnpXloLbeTyyG2sOyhgmdanvD0D0rYduWB3M55GBycmscY_0zG0gjLIl1AgOvBkkd8ZFnbrIcHFseJbQjL_HCrteH01CHlaui6SO4peJTltI5ba_Pnptx8_9zAMKzHalCi1eYdACzF4oBZQ5imah38gwmcxAEgGZYg1iAsXmF-RV09pmgNh26M_6OfJl7R-xVPq-sr_W3_Cv7H_7VpyH_v-Ff8sS6SvmRxYvPr199IQedoYgQAAA/g7kOaY4tZIR6JV2IW3GPVCW1vM9NDJizHWn6xRgNcfM</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ6CMBBF7zJrQ0HFtE2Ma_degExbiwXalJkFIdzdWRiX_728vwODhUhUVqvUyqXkSs24OO9dg3lWEVWojzjdQ4UTzGB3GBAzL_R0Ul6N0RfdmptInEZMr1gzv6Moquz_dCte0O9fKCWZXTr3n95wThSSbjs4ji80zklxkAAAAA/ZGLmCAo0WH_W7lRfc7eTjaboRPu99mdg_ATedGSl06k</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Ne correspond pas</t>
+          <t>Conditions d'utilisation</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QTW-jMBRF_4sXsyoNhjTgSNUon0oLqCREJbBBxhhwAJsakzRU_e-lWcxi3uZJ51zpSvcL9GAOSqXabj6ZNFiR8pHxjNLskYhmwviFKayY4N2EC6UxrqiknaLZX1U9w8p4Oj-hXtR519g6_MN4Lp4XvxftQy91PdNd4EoPpwbaQtZ_fK4TrxUXafrb6z5YXaNTo0XEsYa2L3ciJGGgy6Il0NIXxz6Fp_3p_bYZ_Be-M1HBdu5QQGTbIXo_Hqg02s5723iZvdRXMMjhOg5mK9M9pDffqcLDpYixJm6vm3gY4rXDcLok1jXyBycwWrrixIxUsPmsExw559q7Kiue-qXcuoOXiLX1ZrBlF4AH0ID5F8CEiJ6rl2wca4qQbdo6mo0SF8WrSO8Y6oaOkDGzIRwFqRmpjqUUfVGOUsme_qO3lo4oxZl233vkuRRjDTiLlBk4Gd9daLnUtoeENpjVY0hVvy3_TQ6-v38Ahb2VDcMBAAA/qIQGFJ8S3MYCKpJY6wByJKkNuhsYYJoarn02icHYuSo</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MQQ7CIBBF7zJuTWnVGiAxrt17gQaGUoFOQ4eFaXp36cblfy_vb1BAg2deVi2Ey800W0TbGEoi4jjEp48Pl09MK5whgd5gMIbKzC9bw5tS8ipbda_SxMmEt89URl8V54J_-l3wQJjTccOhji5c-k-vCgV2QbYd7PsPAoGg7o0AAAA/tS4HYPhGyDjc0--pJsMK92Qei0Fk_fzvewE9cKrsatg</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr"/>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Modifier le profil</t>
+          <t>Voir l'emploi</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_0sGp8av1mIE6SZ0le4S89HEJL4Sk6GI_70ZSqeDu4e7O1BEHVIhbHtXFJsHqa3I9cqF4DkD95AeXL_ArGs6JXE0MIWlx8M4CUe1zRj0w5gp20uPLsih7kCUMYhrePJUfSOkvbYluaeQWc3MS3mIb5Wi4KP4u59NJGt31Acs0_hMmcGC64B_pxIZTEIqUzdLQyJYubu2rNB5fgGcNPqHxQAAAA/_sFa1NJXS6WPLM_srUcDZIQ2pkz62iGyDzHAXiWy65w</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_32TWcurSBCG_0tgcjWezyUa-4MwxC1uUaNZNDfSrh33NRoP57-PZwbmcuiChuctqqDg-bkZN98bNAxN__31lXQ_XlUUx9GPsC6_GpjGMPoKi_yvpKvLQ1YHLxL661fCIURY0mGS7cclfBXbrBvyA42FJSKw9eUkndGA6pqEJFmcwfYhYHEWMvsdk9AA7rZlfei2MDpgjOEVQZIbOCdV3BWkLi1qLRwNI39zyfnMql2cl7mdOsZyGTI2nd_2XmXmW9QHSUg_osEMxDYBw3C-OsxlMHzEzEXylPOoaxZRhOLIoNv-7c0e18iFIzWCnkwXB9z1UZxpam7O3lUJqomiSNJJztaLiYiFkywJPDtlN4fmMvj2jcRvsiBxvFnTAMMNPaKNKgj0ktRAoyuK5UFPTU-e_WxhXN2PEkJ0dclNlXbE59hDYpLMZVJNHJSUxhNHS8dPHLra-_ImH83F9O-2O002y8h2eNvZIYFrEnYPjhpzXALtU6qfsyPLk98JttV1OCsntpPapMg8p8LSab56GLhm0qJ5TTUeOA7k73ofqmF6cemUp9772YcT2PmVXqDZ7k8zvyhFzLafu3CR2OwIxB1qQx9l3lMNAC43KuWwS2oiSsDy1kScV5Xvq5WAMLahJt1zBlHM20rrSnWhJB6veuWUrIiglz4NpGge0dbBXZOTJW5CfQ7myY8yVp4eAffaZ-K7UfNcDWcHsDEYslE6fU4WjgTKx85C32FEsczrPad-51hty42ByJ0CGz_ikS2MetWReSsGyDaUS90zlmDnUAl6FtFcT8pSa7tjf8vvrsy7UawVZICk6nqZbINn_DZ9xcv7lO0lrptVF4EMSdFoKkNBilcrI9vB5y4ule4Zci8IRLPQTBufBz6lo46KFyUb-UGp21ft5VJ3bDFaPgnCagkNZEH51OrrdHFnpXloLbeTyyG2sOyhgmdanvD0D0rYduWB3M55GBycmscY_0zG0gjLIl1AgOvBkkd8ZFnbrIcHFseJbQjL_HCrteH01CHlaui6SO4peJTltI5ba_Pnptx8_9zAMKzHalCi1eYdACzF4oBZQ5imah38gwmcxAEgGZYg1iAsXmF-RV09pmgNh26M_6OfJl7R-xVPq-sr_W3_Cv7H_7VpyH_v-Ff8sS6SvmRxYvPr199IQedoYgQAAA/g7kOaY4tZIR6JV2IW3GPVCW1vM9NDJizHWn6xRgNcfM</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr"/>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Suspendre ces emails</t>
+          <t>Ne correspond pas</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qy26CQABF_4VFV1UYUAET0yhgtEBEMSJsDAwII4-ZwowIxn8v7aKL3t09Z3eeHOPmXEYpaeY8X4YUZmNUxUkSjyEueVTdEQ0pwlXDk5A1yQfNFyAXp7epynBxbUpFAG-ouuLF8mf-3rMjy5asZZgL3kRU1wCxr4d-sQm-15Kzbveu1vrncuRDU-4JyzbYg54r1CmBQBaWRxaB8_586oze2VYbSU3RxupToCqKp56Oh6QWSWPvDDtWVoIG3CvQA3emSdYh6hwz9w73NAhHuPs0gr4PdBOF0QrKre_0piuSRKug5FPXeBSX0Ddvhd1SOZg4Wb22evuCdXknolXjcu9cyc2fXAghZhXdxkOjiaoqkiKos0HCAsH8mNWYpdmgaM2SP9qRZEC_sQZG8-H8D8a9Xt8A1uM6eAEAAA/Ca2eUcRhZQJI404p3Ce3h5Q02xN4mYliLjWWdj4dnw8</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12QTW-jMBRF_4sXsyoNhjTgSNUon0oLqCREJbBBxhhwAJsakzRU_e-lWcxi3uZJ51zpSvcL9GAOSqXabj6ZNFiR8pHxjNLskYhmwviFKayY4N2EC6UxrqiknaLZX1U9w8p4Oj-hXtR519g6_MN4Lp4XvxftQy91PdNd4EoPpwbaQtZ_fK4TrxUXafrb6z5YXaNTo0XEsYa2L3ciJGGgy6Il0NIXxz6Fp_3p_bYZ_Be-M1HBdu5QQGTbIXo_Hqg02s5723iZvdRXMMjhOg5mK9M9pDffqcLDpYixJm6vm3gY4rXDcLok1jXyBycwWrrixIxUsPmsExw559q7Kiue-qXcuoOXiLX1ZrBlF4AH0ID5F8CEiJ6rl2wca4qQbdo6mo0SF8WrSO8Y6oaOkDGzIRwFqRmpjqUUfVGOUsme_qO3lo4oxZl233vkuRRjDTiLlBk4Gd9daLnUtoeENpjVY0hVvy3_TQ6-v38Ahb2VDcMBAAA/qIQGFJ8S3MYCKpJY6wByJKkNuhsYYJoarn02icHYuSo</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Centre d'aide</t>
+          <t>Modifier le profil</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2Myw7CIBBF_2XWprRqDZAY1-79AcNDKlAIzCxM0393FsblPSfnbkCgISDWroXoVGtpOCyrdc4OpmQRjPDtFtLVNzhABr3B05hCK94tl2el5EmO6sLSpMXER2iFXoEVNnJ_-qmO0e-fKUaeUzzO71lRSb5nOU6w71_PtShGkAAAAA/4P4WmN-0JrqxfhJveieZ8tWE76bcbxu8MOO8mC9yL0U</t>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2OPQuDMBiE_0sGp8av1mIE6SZ0le4S89HEJL4Sk6GI_70ZSqeDu4e7O1BEHVIhbHtXFJsHqa3I9cqF4DkD95AeXL_ArGs6JXE0MIWlx8M4CUe1zRj0w5gp20uPLsih7kCUMYhrePJUfSOkvbYluaeQWc3MS3mIb5Wi4KP4u59NJGt31Acs0_hMmcGC64B_pxIZTEIqUzdLQyJYubu2rNB5fgGcNPqHxQAAAA/_sFa1NJXS6WPLM_srUcDZIQ2pkz62iGyDzHAXiWy65w</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr"/>
@@ -7482,20 +7482,66 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
+          <t>Suspendre ces emails</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_12Qy26CQABF_4VFV1UYUAET0yhgtEBEMSJsDAwII4-ZwowIxn8v7aKL3t09Z3eeHOPmXEYpaeY8X4YUZmNUxUkSjyEueVTdEQ0pwlXDk5A1yQfNFyAXp7epynBxbUpFAG-ouuLF8mf-3rMjy5asZZgL3kRU1wCxr4d-sQm-15Kzbveu1vrncuRDU-4JyzbYg54r1CmBQBaWRxaB8_586oze2VYbSU3RxupToCqKp56Oh6QWSWPvDDtWVoIG3CvQA3emSdYh6hwz9w73NAhHuPs0gr4PdBOF0QrKre_0piuSRKug5FPXeBSX0Ddvhd1SOZg4Wb22evuCdXknolXjcu9cyc2fXAghZhXdxkOjiaoqkiKos0HCAsH8mNWYpdmgaM2SP9qRZEC_sQZG8-H8D8a9Xt8A1uM6eAEAAA/Ca2eUcRhZQJI404p3Ce3h5Q02xN4mYliLjWWdj4dnw8</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 07:39</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Centre d'aide</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2Myw7CIBBF_2XWprRqDZAY1-79AcNDKlAIzCxM0393FsblPSfnbkCgISDWroXoVGtpOCyrdc4OpmQRjPDtFtLVNzhABr3B05hCK94tl2el5EmO6sLSpMXER2iFXoEVNnJ_-qmO0e-fKUaeUzzO71lRSb5nOU6w71_PtShGkAAAAA/4P4WmN-0JrqxfhJveieZ8tWE76bcbxu8MOO8mC9yL0U</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 07:39</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
           <t>Conditions d'utilisation</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr">
+      <c r="C309" s="2" t="inlineStr">
         <is>
           <t>Alerte email — Indeed &lt;donotreply@match.indeed.com&gt;</t>
         </is>
       </c>
-      <c r="D307" s="2" t="inlineStr">
+      <c r="D309" s="2" t="inlineStr">
         <is>
           <t>https://cts.indeed.com/v3/H4sIAAAAAAAA_z2MwQ6DIBAF_2V7bUTb2gBJ03Pv_oCBRSwgBpaDMf578dLjm8m8HQpIsERrloyZ1MyLRtSNioF5nEb_tv5l0oVihisEkDuMSsWy0EfX8CEEv_NWPKtUflZusCmWyVZFqeCfbiueCFM4b8jV0blb_-1Fid7kwNsOjuMH-frB2Y0AAAA/e0qqxOPFQI21Ma3LJ_ywjhkdOVcqOEfuZ2rNUuqzsZg</t>
         </is>
       </c>
-      <c r="E307" s="2" t="inlineStr"/>
+      <c r="E309" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
